--- a/server/excel/release/divine-dragon.xlsx
+++ b/server/excel/release/divine-dragon.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">升星御灵等级要求</t>
   </si>
   <si>
-    <t xml:space="preserve">Mai Siêu Phong · Phá</t>
+    <t xml:space="preserve">Hải Quái-Phá</t>
   </si>
   <si>
     <t xml:space="preserve">1:10000#28:75</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">3:200101:500#3:200105:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiểu Long Nữ · Phá</t>
+    <t xml:space="preserve">Mohmoo-Phá</t>
   </si>
   <si>
     <t xml:space="preserve">20:10101:1</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">3:200101:1000#3:200109:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Lục Ngạc · Phá</t>
+    <t xml:space="preserve">Laboon-Phá</t>
   </si>
   <si>
     <t xml:space="preserve">20:10201:1</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">3:200101:2500#3:200113:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Quách Tương · Phá</t>
+    <t xml:space="preserve">Rồng Lửa-Phá</t>
   </si>
   <si>
     <t xml:space="preserve">20:10301:1</t>
@@ -737,6 +737,9 @@
     <t xml:space="preserve">3:200101:17000#3:200120:170</t>
   </si>
   <si>
+    <t xml:space="preserve">Rồng Lửa-Công</t>
+  </si>
+  <si>
     <t xml:space="preserve">1:12000000#28:80000</t>
   </si>
   <si>
@@ -1004,7 +1007,7 @@
     <t xml:space="preserve">3:200101:47000#3:200120:320</t>
   </si>
   <si>
-    <t xml:space="preserve">Mai Siêu Phong-Miễn</t>
+    <t xml:space="preserve">Hải Quái-Miễn</t>
   </si>
   <si>
     <t xml:space="preserve">20:20001:1</t>
@@ -1079,7 +1082,7 @@
     <t xml:space="preserve">3:200101:500#3:200106:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiểu Long Nữ-Miễn</t>
+    <t xml:space="preserve">Mohmoo-Miễn</t>
   </si>
   <si>
     <t xml:space="preserve">20:20101:1</t>
@@ -1154,7 +1157,7 @@
     <t xml:space="preserve">3:200101:1000#3:200110:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Lục Ngạc-Miễn</t>
+    <t xml:space="preserve">Laboon-Miễn</t>
   </si>
   <si>
     <t xml:space="preserve">20:20201:1</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">3:200101:2500#3:200114:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Quách Tương-Miễn</t>
+    <t xml:space="preserve">Rồng Lửa-Miễn</t>
   </si>
   <si>
     <t xml:space="preserve">20:20301:1</t>
@@ -1394,7 +1397,7 @@
     <t xml:space="preserve">20:20301:34</t>
   </si>
   <si>
-    <t xml:space="preserve">Mai Siêu Phong-Thuẫn</t>
+    <t xml:space="preserve">Hải Quái-Thuẫn</t>
   </si>
   <si>
     <t xml:space="preserve">20:30001:1</t>
@@ -1469,7 +1472,7 @@
     <t xml:space="preserve">3:200101:500#3:200107:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiểu Long Nữ-Thuẫn</t>
+    <t xml:space="preserve">Mohmoo-Thuẫn</t>
   </si>
   <si>
     <t xml:space="preserve">20:30101:1</t>
@@ -1544,7 +1547,7 @@
     <t xml:space="preserve">3:200101:1000#3:200111:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Lục Ngạc-Thuẫn</t>
+    <t xml:space="preserve">Laboon-Thuẫn</t>
   </si>
   <si>
     <t xml:space="preserve">20:30201:1</t>
@@ -1619,7 +1622,7 @@
     <t xml:space="preserve">3:200101:2500#3:200115:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Quách Tương-Thuẫn</t>
+    <t xml:space="preserve">Rồng Lửa-Thuẫn</t>
   </si>
   <si>
     <t xml:space="preserve">20:30301:1</t>
@@ -1784,7 +1787,7 @@
     <t xml:space="preserve">20:30301:34</t>
   </si>
   <si>
-    <t xml:space="preserve">Mai Siêu Phong-Trợ</t>
+    <t xml:space="preserve">Hải Quái-Công</t>
   </si>
   <si>
     <t xml:space="preserve">20:40001:1</t>
@@ -1859,7 +1862,7 @@
     <t xml:space="preserve">3:200101:500#3:200108:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiểu Long Nữ-Trợ</t>
+    <t xml:space="preserve">Mohmoo-Công</t>
   </si>
   <si>
     <t xml:space="preserve">20:40101:1</t>
@@ -1934,7 +1937,7 @@
     <t xml:space="preserve">3:200101:1000#3:200112:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Lục Ngạc-Trợ</t>
+    <t xml:space="preserve">Laboon-Công</t>
   </si>
   <si>
     <t xml:space="preserve">20:40201:1</t>
@@ -2007,9 +2010,6 @@
   </si>
   <si>
     <t xml:space="preserve">3:200101:2500#3:200116:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quách Tương-Trợ</t>
   </si>
   <si>
     <t xml:space="preserve">20:40301:1</t>
@@ -8316,7 +8316,7 @@
         <v>51</v>
       </c>
       <c r="E112" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F112" t="n">
         <v>5</v>
@@ -8328,16 +8328,16 @@
         <v>92010010</v>
       </c>
       <c r="I112" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J112" t="n">
         <v>2000000</v>
       </c>
       <c r="K112" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L112" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M112" t="n">
         <v>100</v>
@@ -8360,7 +8360,7 @@
         <v>52</v>
       </c>
       <c r="E113" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F113" t="n">
         <v>5</v>
@@ -8372,16 +8372,16 @@
         <v>92010010</v>
       </c>
       <c r="I113" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J113" t="n">
         <v>2100000</v>
       </c>
       <c r="K113" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L113" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M113" t="n">
         <v>100</v>
@@ -8404,7 +8404,7 @@
         <v>53</v>
       </c>
       <c r="E114" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F114" t="n">
         <v>5</v>
@@ -8416,16 +8416,16 @@
         <v>92010010</v>
       </c>
       <c r="I114" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J114" t="n">
         <v>2200000</v>
       </c>
       <c r="K114" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L114" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M114" t="n">
         <v>100</v>
@@ -8448,7 +8448,7 @@
         <v>54</v>
       </c>
       <c r="E115" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F115" t="n">
         <v>5</v>
@@ -8460,16 +8460,16 @@
         <v>92010010</v>
       </c>
       <c r="I115" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J115" t="n">
         <v>2300000</v>
       </c>
       <c r="K115" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L115" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M115" t="n">
         <v>100</v>
@@ -8492,7 +8492,7 @@
         <v>55</v>
       </c>
       <c r="E116" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F116" t="n">
         <v>5</v>
@@ -8504,16 +8504,16 @@
         <v>92010010</v>
       </c>
       <c r="I116" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J116" t="n">
         <v>2400000</v>
       </c>
       <c r="K116" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L116" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M116" t="n">
         <v>100</v>
@@ -8536,7 +8536,7 @@
         <v>56</v>
       </c>
       <c r="E117" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F117" t="n">
         <v>5</v>
@@ -8548,16 +8548,16 @@
         <v>92010010</v>
       </c>
       <c r="I117" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J117" t="n">
         <v>2500000</v>
       </c>
       <c r="K117" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L117" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M117" t="n">
         <v>100</v>
@@ -8580,7 +8580,7 @@
         <v>57</v>
       </c>
       <c r="E118" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F118" t="n">
         <v>5</v>
@@ -8592,16 +8592,16 @@
         <v>92010010</v>
       </c>
       <c r="I118" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J118" t="n">
         <v>2600000</v>
       </c>
       <c r="K118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L118" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M118" t="n">
         <v>100</v>
@@ -8624,7 +8624,7 @@
         <v>58</v>
       </c>
       <c r="E119" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F119" t="n">
         <v>5</v>
@@ -8636,16 +8636,16 @@
         <v>92010010</v>
       </c>
       <c r="I119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J119" t="n">
         <v>2700000</v>
       </c>
       <c r="K119" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L119" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M119" t="n">
         <v>100</v>
@@ -8668,7 +8668,7 @@
         <v>59</v>
       </c>
       <c r="E120" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F120" t="n">
         <v>5</v>
@@ -8680,16 +8680,16 @@
         <v>92010010</v>
       </c>
       <c r="I120" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J120" t="n">
         <v>2800000</v>
       </c>
       <c r="K120" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L120" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M120" t="n">
         <v>100</v>
@@ -8712,7 +8712,7 @@
         <v>60</v>
       </c>
       <c r="E121" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F121" t="n">
         <v>5</v>
@@ -8724,16 +8724,16 @@
         <v>92010010</v>
       </c>
       <c r="I121" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J121" t="n">
         <v>2900000</v>
       </c>
       <c r="K121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L121" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M121" t="n">
         <v>100</v>
@@ -8756,7 +8756,7 @@
         <v>61</v>
       </c>
       <c r="E122" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F122" t="n">
         <v>5</v>
@@ -8768,16 +8768,16 @@
         <v>92010010</v>
       </c>
       <c r="I122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J122" t="n">
         <v>3000000</v>
       </c>
       <c r="K122" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L122" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M122" t="n">
         <v>100</v>
@@ -8800,7 +8800,7 @@
         <v>62</v>
       </c>
       <c r="E123" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F123" t="n">
         <v>5</v>
@@ -8812,16 +8812,16 @@
         <v>92010010</v>
       </c>
       <c r="I123" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J123" t="n">
         <v>3100000</v>
       </c>
       <c r="K123" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L123" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M123" t="n">
         <v>100</v>
@@ -8844,7 +8844,7 @@
         <v>63</v>
       </c>
       <c r="E124" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F124" t="n">
         <v>5</v>
@@ -8856,16 +8856,16 @@
         <v>92010010</v>
       </c>
       <c r="I124" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J124" t="n">
         <v>3200000</v>
       </c>
       <c r="K124" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L124" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M124" t="n">
         <v>100</v>
@@ -8888,7 +8888,7 @@
         <v>64</v>
       </c>
       <c r="E125" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F125" t="n">
         <v>5</v>
@@ -8900,16 +8900,16 @@
         <v>92010010</v>
       </c>
       <c r="I125" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J125" t="n">
         <v>3300000</v>
       </c>
       <c r="K125" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L125" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M125" t="n">
         <v>100</v>
@@ -8932,7 +8932,7 @@
         <v>65</v>
       </c>
       <c r="E126" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F126" t="n">
         <v>5</v>
@@ -8944,16 +8944,16 @@
         <v>92010010</v>
       </c>
       <c r="I126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J126" t="n">
         <v>3400000</v>
       </c>
       <c r="K126" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L126" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M126" t="n">
         <v>100</v>
@@ -8976,7 +8976,7 @@
         <v>66</v>
       </c>
       <c r="E127" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F127" t="n">
         <v>5</v>
@@ -8988,16 +8988,16 @@
         <v>92010010</v>
       </c>
       <c r="I127" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J127" t="n">
         <v>3500000</v>
       </c>
       <c r="K127" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L127" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M127" t="n">
         <v>100</v>
@@ -9020,7 +9020,7 @@
         <v>67</v>
       </c>
       <c r="E128" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F128" t="n">
         <v>5</v>
@@ -9032,16 +9032,16 @@
         <v>92010010</v>
       </c>
       <c r="I128" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J128" t="n">
         <v>3600000</v>
       </c>
       <c r="K128" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L128" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M128" t="n">
         <v>100</v>
@@ -9064,7 +9064,7 @@
         <v>68</v>
       </c>
       <c r="E129" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F129" t="n">
         <v>5</v>
@@ -9076,16 +9076,16 @@
         <v>92010010</v>
       </c>
       <c r="I129" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J129" t="n">
         <v>3700000</v>
       </c>
       <c r="K129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L129" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M129" t="n">
         <v>100</v>
@@ -9108,7 +9108,7 @@
         <v>69</v>
       </c>
       <c r="E130" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F130" t="n">
         <v>5</v>
@@ -9120,16 +9120,16 @@
         <v>92010010</v>
       </c>
       <c r="I130" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J130" t="n">
         <v>3800000</v>
       </c>
       <c r="K130" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L130" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M130" t="n">
         <v>100</v>
@@ -9152,7 +9152,7 @@
         <v>70</v>
       </c>
       <c r="E131" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F131" t="n">
         <v>5</v>
@@ -9164,16 +9164,16 @@
         <v>92010010</v>
       </c>
       <c r="I131" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J131" t="n">
         <v>3900000</v>
       </c>
       <c r="K131" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L131" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M131" t="n">
         <v>100</v>
@@ -9196,7 +9196,7 @@
         <v>71</v>
       </c>
       <c r="E132" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F132" t="n">
         <v>5</v>
@@ -9208,16 +9208,16 @@
         <v>92010010</v>
       </c>
       <c r="I132" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J132" t="n">
         <v>4000000</v>
       </c>
       <c r="K132" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M132" t="n">
         <v>100</v>
@@ -9240,7 +9240,7 @@
         <v>72</v>
       </c>
       <c r="E133" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F133" t="n">
         <v>5</v>
@@ -9252,16 +9252,16 @@
         <v>92010010</v>
       </c>
       <c r="I133" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J133" t="n">
         <v>4100000</v>
       </c>
       <c r="K133" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L133" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M133" t="n">
         <v>100</v>
@@ -9284,7 +9284,7 @@
         <v>73</v>
       </c>
       <c r="E134" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F134" t="n">
         <v>5</v>
@@ -9296,16 +9296,16 @@
         <v>92010010</v>
       </c>
       <c r="I134" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J134" t="n">
         <v>4200000</v>
       </c>
       <c r="K134" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L134" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M134" t="n">
         <v>100</v>
@@ -9328,7 +9328,7 @@
         <v>74</v>
       </c>
       <c r="E135" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F135" t="n">
         <v>5</v>
@@ -9340,16 +9340,16 @@
         <v>92010010</v>
       </c>
       <c r="I135" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J135" t="n">
         <v>4300000</v>
       </c>
       <c r="K135" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L135" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M135" t="n">
         <v>100</v>
@@ -9372,7 +9372,7 @@
         <v>75</v>
       </c>
       <c r="E136" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F136" t="n">
         <v>5</v>
@@ -9384,16 +9384,16 @@
         <v>92010010</v>
       </c>
       <c r="I136" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J136" t="n">
         <v>4400000</v>
       </c>
       <c r="K136" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L136" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M136" t="n">
         <v>100</v>
@@ -9416,7 +9416,7 @@
         <v>76</v>
       </c>
       <c r="E137" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F137" t="n">
         <v>5</v>
@@ -9428,16 +9428,16 @@
         <v>92010010</v>
       </c>
       <c r="I137" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J137" t="n">
         <v>4500000</v>
       </c>
       <c r="K137" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L137" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M137" t="n">
         <v>100</v>
@@ -9460,7 +9460,7 @@
         <v>77</v>
       </c>
       <c r="E138" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F138" t="n">
         <v>5</v>
@@ -9472,16 +9472,16 @@
         <v>92010010</v>
       </c>
       <c r="I138" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J138" t="n">
         <v>4600000</v>
       </c>
       <c r="K138" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L138" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M138" t="n">
         <v>100</v>
@@ -9504,7 +9504,7 @@
         <v>78</v>
       </c>
       <c r="E139" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F139" t="n">
         <v>5</v>
@@ -9516,16 +9516,16 @@
         <v>92010010</v>
       </c>
       <c r="I139" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J139" t="n">
         <v>4700000</v>
       </c>
       <c r="K139" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L139" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M139" t="n">
         <v>100</v>
@@ -9548,7 +9548,7 @@
         <v>79</v>
       </c>
       <c r="E140" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F140" t="n">
         <v>5</v>
@@ -9560,16 +9560,16 @@
         <v>92010010</v>
       </c>
       <c r="I140" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J140" t="n">
         <v>4800000</v>
       </c>
       <c r="K140" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L140" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M140" t="n">
         <v>100</v>
@@ -9592,7 +9592,7 @@
         <v>80</v>
       </c>
       <c r="E141" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="F141" t="n">
         <v>5</v>
@@ -9604,7 +9604,7 @@
         <v>92010010</v>
       </c>
       <c r="I141" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J141" t="n">
         <v>4900000</v>
@@ -9613,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="L141" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -9636,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F142" t="n">
         <v>2</v>
@@ -9654,10 +9654,10 @@
         <v>2700</v>
       </c>
       <c r="K142" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L142" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M142" t="n">
         <v>100</v>
@@ -9680,7 +9680,7 @@
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F143" t="n">
         <v>2</v>
@@ -9698,10 +9698,10 @@
         <v>5400</v>
       </c>
       <c r="K143" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L143" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M143" t="n">
         <v>100</v>
@@ -9724,7 +9724,7 @@
         <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F144" t="n">
         <v>2</v>
@@ -9742,10 +9742,10 @@
         <v>8100</v>
       </c>
       <c r="K144" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L144" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M144" t="n">
         <v>100</v>
@@ -9768,7 +9768,7 @@
         <v>4</v>
       </c>
       <c r="E145" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F145" t="n">
         <v>2</v>
@@ -9786,10 +9786,10 @@
         <v>10800</v>
       </c>
       <c r="K145" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L145" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M145" t="n">
         <v>100</v>
@@ -9812,7 +9812,7 @@
         <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F146" t="n">
         <v>2</v>
@@ -9830,10 +9830,10 @@
         <v>13500</v>
       </c>
       <c r="K146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L146" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M146" t="n">
         <v>100</v>
@@ -9856,7 +9856,7 @@
         <v>6</v>
       </c>
       <c r="E147" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F147" t="n">
         <v>2</v>
@@ -9874,10 +9874,10 @@
         <v>18900</v>
       </c>
       <c r="K147" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L147" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M147" t="n">
         <v>100</v>
@@ -9900,7 +9900,7 @@
         <v>7</v>
       </c>
       <c r="E148" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F148" t="n">
         <v>2</v>
@@ -9918,10 +9918,10 @@
         <v>24300</v>
       </c>
       <c r="K148" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L148" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M148" t="n">
         <v>100</v>
@@ -9944,7 +9944,7 @@
         <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F149" t="n">
         <v>2</v>
@@ -9962,10 +9962,10 @@
         <v>29700</v>
       </c>
       <c r="K149" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L149" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M149" t="n">
         <v>100</v>
@@ -9988,7 +9988,7 @@
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F150" t="n">
         <v>2</v>
@@ -10006,10 +10006,10 @@
         <v>35100</v>
       </c>
       <c r="K150" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L150" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M150" t="n">
         <v>100</v>
@@ -10032,7 +10032,7 @@
         <v>10</v>
       </c>
       <c r="E151" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F151" t="n">
         <v>2</v>
@@ -10050,10 +10050,10 @@
         <v>40500</v>
       </c>
       <c r="K151" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L151" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M151" t="n">
         <v>100</v>
@@ -10076,7 +10076,7 @@
         <v>11</v>
       </c>
       <c r="E152" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F152" t="n">
         <v>2</v>
@@ -10094,10 +10094,10 @@
         <v>48600</v>
       </c>
       <c r="K152" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L152" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M152" t="n">
         <v>100</v>
@@ -10120,7 +10120,7 @@
         <v>12</v>
       </c>
       <c r="E153" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F153" t="n">
         <v>2</v>
@@ -10138,10 +10138,10 @@
         <v>56700</v>
       </c>
       <c r="K153" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L153" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M153" t="n">
         <v>100</v>
@@ -10164,7 +10164,7 @@
         <v>13</v>
       </c>
       <c r="E154" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F154" t="n">
         <v>2</v>
@@ -10182,10 +10182,10 @@
         <v>64800</v>
       </c>
       <c r="K154" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L154" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M154" t="n">
         <v>100</v>
@@ -10208,7 +10208,7 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F155" t="n">
         <v>2</v>
@@ -10226,10 +10226,10 @@
         <v>72900</v>
       </c>
       <c r="K155" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L155" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M155" t="n">
         <v>100</v>
@@ -10252,7 +10252,7 @@
         <v>15</v>
       </c>
       <c r="E156" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F156" t="n">
         <v>2</v>
@@ -10270,10 +10270,10 @@
         <v>81000</v>
       </c>
       <c r="K156" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L156" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M156" t="n">
         <v>100</v>
@@ -10296,7 +10296,7 @@
         <v>16</v>
       </c>
       <c r="E157" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F157" t="n">
         <v>2</v>
@@ -10314,10 +10314,10 @@
         <v>91800</v>
       </c>
       <c r="K157" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L157" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M157" t="n">
         <v>100</v>
@@ -10340,7 +10340,7 @@
         <v>17</v>
       </c>
       <c r="E158" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F158" t="n">
         <v>2</v>
@@ -10358,10 +10358,10 @@
         <v>102600</v>
       </c>
       <c r="K158" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L158" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M158" t="n">
         <v>100</v>
@@ -10384,7 +10384,7 @@
         <v>18</v>
       </c>
       <c r="E159" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F159" t="n">
         <v>2</v>
@@ -10402,10 +10402,10 @@
         <v>113400</v>
       </c>
       <c r="K159" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L159" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M159" t="n">
         <v>100</v>
@@ -10428,7 +10428,7 @@
         <v>19</v>
       </c>
       <c r="E160" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F160" t="n">
         <v>2</v>
@@ -10446,10 +10446,10 @@
         <v>124200</v>
       </c>
       <c r="K160" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L160" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M160" t="n">
         <v>100</v>
@@ -10472,7 +10472,7 @@
         <v>20</v>
       </c>
       <c r="E161" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F161" t="n">
         <v>2</v>
@@ -10493,7 +10493,7 @@
         <v>98</v>
       </c>
       <c r="L161" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -10516,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F162" t="n">
         <v>3</v>
@@ -10534,10 +10534,10 @@
         <v>5400</v>
       </c>
       <c r="K162" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L162" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M162" t="n">
         <v>100</v>
@@ -10560,7 +10560,7 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F163" t="n">
         <v>3</v>
@@ -10578,10 +10578,10 @@
         <v>10800</v>
       </c>
       <c r="K163" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L163" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M163" t="n">
         <v>100</v>
@@ -10604,7 +10604,7 @@
         <v>3</v>
       </c>
       <c r="E164" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F164" t="n">
         <v>3</v>
@@ -10622,10 +10622,10 @@
         <v>16200</v>
       </c>
       <c r="K164" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L164" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M164" t="n">
         <v>100</v>
@@ -10648,7 +10648,7 @@
         <v>4</v>
       </c>
       <c r="E165" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F165" t="n">
         <v>3</v>
@@ -10666,10 +10666,10 @@
         <v>21600</v>
       </c>
       <c r="K165" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L165" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M165" t="n">
         <v>100</v>
@@ -10692,7 +10692,7 @@
         <v>5</v>
       </c>
       <c r="E166" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F166" t="n">
         <v>3</v>
@@ -10710,10 +10710,10 @@
         <v>27000</v>
       </c>
       <c r="K166" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L166" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M166" t="n">
         <v>100</v>
@@ -10736,7 +10736,7 @@
         <v>6</v>
       </c>
       <c r="E167" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F167" t="n">
         <v>3</v>
@@ -10754,10 +10754,10 @@
         <v>37800</v>
       </c>
       <c r="K167" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L167" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M167" t="n">
         <v>100</v>
@@ -10780,7 +10780,7 @@
         <v>7</v>
       </c>
       <c r="E168" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F168" t="n">
         <v>3</v>
@@ -10798,10 +10798,10 @@
         <v>48600</v>
       </c>
       <c r="K168" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L168" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M168" t="n">
         <v>100</v>
@@ -10824,7 +10824,7 @@
         <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F169" t="n">
         <v>3</v>
@@ -10842,10 +10842,10 @@
         <v>59400</v>
       </c>
       <c r="K169" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L169" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M169" t="n">
         <v>100</v>
@@ -10868,7 +10868,7 @@
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F170" t="n">
         <v>3</v>
@@ -10886,10 +10886,10 @@
         <v>70200</v>
       </c>
       <c r="K170" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L170" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M170" t="n">
         <v>100</v>
@@ -10912,7 +10912,7 @@
         <v>10</v>
       </c>
       <c r="E171" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F171" t="n">
         <v>3</v>
@@ -10930,10 +10930,10 @@
         <v>81000</v>
       </c>
       <c r="K171" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L171" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M171" t="n">
         <v>100</v>
@@ -10956,7 +10956,7 @@
         <v>11</v>
       </c>
       <c r="E172" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F172" t="n">
         <v>3</v>
@@ -10974,10 +10974,10 @@
         <v>97200</v>
       </c>
       <c r="K172" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L172" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M172" t="n">
         <v>100</v>
@@ -11000,7 +11000,7 @@
         <v>12</v>
       </c>
       <c r="E173" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F173" t="n">
         <v>3</v>
@@ -11018,10 +11018,10 @@
         <v>113400</v>
       </c>
       <c r="K173" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L173" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M173" t="n">
         <v>100</v>
@@ -11044,7 +11044,7 @@
         <v>13</v>
       </c>
       <c r="E174" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F174" t="n">
         <v>3</v>
@@ -11062,10 +11062,10 @@
         <v>129600</v>
       </c>
       <c r="K174" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L174" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M174" t="n">
         <v>100</v>
@@ -11088,7 +11088,7 @@
         <v>14</v>
       </c>
       <c r="E175" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F175" t="n">
         <v>3</v>
@@ -11106,10 +11106,10 @@
         <v>145800</v>
       </c>
       <c r="K175" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L175" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M175" t="n">
         <v>100</v>
@@ -11132,7 +11132,7 @@
         <v>15</v>
       </c>
       <c r="E176" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F176" t="n">
         <v>3</v>
@@ -11150,10 +11150,10 @@
         <v>162000</v>
       </c>
       <c r="K176" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L176" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M176" t="n">
         <v>100</v>
@@ -11176,7 +11176,7 @@
         <v>16</v>
       </c>
       <c r="E177" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F177" t="n">
         <v>3</v>
@@ -11194,10 +11194,10 @@
         <v>183600</v>
       </c>
       <c r="K177" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L177" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M177" t="n">
         <v>100</v>
@@ -11220,7 +11220,7 @@
         <v>17</v>
       </c>
       <c r="E178" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F178" t="n">
         <v>3</v>
@@ -11238,10 +11238,10 @@
         <v>205200</v>
       </c>
       <c r="K178" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L178" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M178" t="n">
         <v>100</v>
@@ -11264,7 +11264,7 @@
         <v>18</v>
       </c>
       <c r="E179" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F179" t="n">
         <v>3</v>
@@ -11282,10 +11282,10 @@
         <v>226800</v>
       </c>
       <c r="K179" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L179" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M179" t="n">
         <v>100</v>
@@ -11308,7 +11308,7 @@
         <v>19</v>
       </c>
       <c r="E180" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F180" t="n">
         <v>3</v>
@@ -11326,10 +11326,10 @@
         <v>248400</v>
       </c>
       <c r="K180" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L180" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M180" t="n">
         <v>100</v>
@@ -11352,7 +11352,7 @@
         <v>20</v>
       </c>
       <c r="E181" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F181" t="n">
         <v>3</v>
@@ -11373,7 +11373,7 @@
         <v>98</v>
       </c>
       <c r="L181" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F182" t="n">
         <v>4</v>
@@ -11414,10 +11414,10 @@
         <v>8100</v>
       </c>
       <c r="K182" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L182" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M182" t="n">
         <v>100</v>
@@ -11440,7 +11440,7 @@
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F183" t="n">
         <v>4</v>
@@ -11458,10 +11458,10 @@
         <v>16200</v>
       </c>
       <c r="K183" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L183" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M183" t="n">
         <v>100</v>
@@ -11484,7 +11484,7 @@
         <v>3</v>
       </c>
       <c r="E184" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F184" t="n">
         <v>4</v>
@@ -11502,10 +11502,10 @@
         <v>24300</v>
       </c>
       <c r="K184" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L184" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M184" t="n">
         <v>100</v>
@@ -11528,7 +11528,7 @@
         <v>4</v>
       </c>
       <c r="E185" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F185" t="n">
         <v>4</v>
@@ -11546,10 +11546,10 @@
         <v>32400</v>
       </c>
       <c r="K185" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L185" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M185" t="n">
         <v>100</v>
@@ -11572,7 +11572,7 @@
         <v>5</v>
       </c>
       <c r="E186" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F186" t="n">
         <v>4</v>
@@ -11590,10 +11590,10 @@
         <v>40500</v>
       </c>
       <c r="K186" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L186" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M186" t="n">
         <v>100</v>
@@ -11616,7 +11616,7 @@
         <v>6</v>
       </c>
       <c r="E187" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F187" t="n">
         <v>4</v>
@@ -11634,10 +11634,10 @@
         <v>56700</v>
       </c>
       <c r="K187" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L187" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M187" t="n">
         <v>100</v>
@@ -11660,7 +11660,7 @@
         <v>7</v>
       </c>
       <c r="E188" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F188" t="n">
         <v>4</v>
@@ -11678,10 +11678,10 @@
         <v>72900</v>
       </c>
       <c r="K188" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L188" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M188" t="n">
         <v>100</v>
@@ -11704,7 +11704,7 @@
         <v>8</v>
       </c>
       <c r="E189" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F189" t="n">
         <v>4</v>
@@ -11722,10 +11722,10 @@
         <v>89100</v>
       </c>
       <c r="K189" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L189" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M189" t="n">
         <v>100</v>
@@ -11748,7 +11748,7 @@
         <v>9</v>
       </c>
       <c r="E190" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F190" t="n">
         <v>4</v>
@@ -11766,10 +11766,10 @@
         <v>105300</v>
       </c>
       <c r="K190" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L190" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M190" t="n">
         <v>100</v>
@@ -11792,7 +11792,7 @@
         <v>10</v>
       </c>
       <c r="E191" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F191" t="n">
         <v>4</v>
@@ -11810,10 +11810,10 @@
         <v>121500</v>
       </c>
       <c r="K191" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L191" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M191" t="n">
         <v>100</v>
@@ -11836,7 +11836,7 @@
         <v>11</v>
       </c>
       <c r="E192" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F192" t="n">
         <v>4</v>
@@ -11854,10 +11854,10 @@
         <v>145800</v>
       </c>
       <c r="K192" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L192" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M192" t="n">
         <v>100</v>
@@ -11881,7 +11881,7 @@
         <v>12</v>
       </c>
       <c r="E193" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F193" t="n">
         <v>4</v>
@@ -11899,10 +11899,10 @@
         <v>170100</v>
       </c>
       <c r="K193" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L193" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M193" t="n">
         <v>100</v>
@@ -11926,7 +11926,7 @@
         <v>13</v>
       </c>
       <c r="E194" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F194" t="n">
         <v>4</v>
@@ -11944,10 +11944,10 @@
         <v>194400</v>
       </c>
       <c r="K194" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L194" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M194" t="n">
         <v>100</v>
@@ -11971,7 +11971,7 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F195" t="n">
         <v>4</v>
@@ -11989,10 +11989,10 @@
         <v>218700</v>
       </c>
       <c r="K195" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L195" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M195" t="n">
         <v>100</v>
@@ -12016,7 +12016,7 @@
         <v>15</v>
       </c>
       <c r="E196" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F196" t="n">
         <v>4</v>
@@ -12034,10 +12034,10 @@
         <v>243000</v>
       </c>
       <c r="K196" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L196" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M196" t="n">
         <v>100</v>
@@ -12061,7 +12061,7 @@
         <v>16</v>
       </c>
       <c r="E197" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F197" t="n">
         <v>4</v>
@@ -12079,10 +12079,10 @@
         <v>275400</v>
       </c>
       <c r="K197" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L197" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M197" t="n">
         <v>100</v>
@@ -12106,7 +12106,7 @@
         <v>17</v>
       </c>
       <c r="E198" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F198" t="n">
         <v>4</v>
@@ -12124,10 +12124,10 @@
         <v>307800</v>
       </c>
       <c r="K198" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L198" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M198" t="n">
         <v>100</v>
@@ -12151,7 +12151,7 @@
         <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F199" t="n">
         <v>4</v>
@@ -12169,10 +12169,10 @@
         <v>340200</v>
       </c>
       <c r="K199" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L199" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M199" t="n">
         <v>100</v>
@@ -12196,7 +12196,7 @@
         <v>19</v>
       </c>
       <c r="E200" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F200" t="n">
         <v>4</v>
@@ -12214,10 +12214,10 @@
         <v>372600</v>
       </c>
       <c r="K200" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L200" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M200" t="n">
         <v>100</v>
@@ -12241,7 +12241,7 @@
         <v>20</v>
       </c>
       <c r="E201" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F201" t="n">
         <v>4</v>
@@ -12262,7 +12262,7 @@
         <v>98</v>
       </c>
       <c r="L201" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M201" t="n">
         <v>0</v>
@@ -12286,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F202" t="n">
         <v>5</v>
@@ -12304,10 +12304,10 @@
         <v>10800</v>
       </c>
       <c r="K202" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L202" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M202" t="n">
         <v>100</v>
@@ -12331,7 +12331,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F203" t="n">
         <v>5</v>
@@ -12349,10 +12349,10 @@
         <v>21600</v>
       </c>
       <c r="K203" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L203" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M203" t="n">
         <v>100</v>
@@ -12376,7 +12376,7 @@
         <v>3</v>
       </c>
       <c r="E204" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F204" t="n">
         <v>5</v>
@@ -12394,10 +12394,10 @@
         <v>32400</v>
       </c>
       <c r="K204" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L204" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M204" t="n">
         <v>100</v>
@@ -12421,7 +12421,7 @@
         <v>4</v>
       </c>
       <c r="E205" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F205" t="n">
         <v>5</v>
@@ -12439,10 +12439,10 @@
         <v>43200</v>
       </c>
       <c r="K205" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L205" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M205" t="n">
         <v>100</v>
@@ -12466,7 +12466,7 @@
         <v>5</v>
       </c>
       <c r="E206" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F206" t="n">
         <v>5</v>
@@ -12484,10 +12484,10 @@
         <v>54000</v>
       </c>
       <c r="K206" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L206" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M206" t="n">
         <v>100</v>
@@ -12511,7 +12511,7 @@
         <v>6</v>
       </c>
       <c r="E207" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F207" t="n">
         <v>5</v>
@@ -12529,10 +12529,10 @@
         <v>75600</v>
       </c>
       <c r="K207" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L207" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M207" t="n">
         <v>100</v>
@@ -12556,7 +12556,7 @@
         <v>7</v>
       </c>
       <c r="E208" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F208" t="n">
         <v>5</v>
@@ -12574,10 +12574,10 @@
         <v>97200</v>
       </c>
       <c r="K208" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L208" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M208" t="n">
         <v>100</v>
@@ -12601,7 +12601,7 @@
         <v>8</v>
       </c>
       <c r="E209" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F209" t="n">
         <v>5</v>
@@ -12619,10 +12619,10 @@
         <v>118800</v>
       </c>
       <c r="K209" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L209" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M209" t="n">
         <v>100</v>
@@ -12646,7 +12646,7 @@
         <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F210" t="n">
         <v>5</v>
@@ -12664,10 +12664,10 @@
         <v>140400</v>
       </c>
       <c r="K210" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L210" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M210" t="n">
         <v>100</v>
@@ -12691,7 +12691,7 @@
         <v>10</v>
       </c>
       <c r="E211" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F211" t="n">
         <v>5</v>
@@ -12709,10 +12709,10 @@
         <v>162000</v>
       </c>
       <c r="K211" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L211" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M211" t="n">
         <v>100</v>
@@ -12736,7 +12736,7 @@
         <v>11</v>
       </c>
       <c r="E212" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F212" t="n">
         <v>5</v>
@@ -12754,10 +12754,10 @@
         <v>194400</v>
       </c>
       <c r="K212" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L212" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M212" t="n">
         <v>100</v>
@@ -12781,7 +12781,7 @@
         <v>12</v>
       </c>
       <c r="E213" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F213" t="n">
         <v>5</v>
@@ -12799,10 +12799,10 @@
         <v>226800</v>
       </c>
       <c r="K213" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L213" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M213" t="n">
         <v>100</v>
@@ -12826,7 +12826,7 @@
         <v>13</v>
       </c>
       <c r="E214" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F214" t="n">
         <v>5</v>
@@ -12844,10 +12844,10 @@
         <v>259200</v>
       </c>
       <c r="K214" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L214" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M214" t="n">
         <v>100</v>
@@ -12871,7 +12871,7 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F215" t="n">
         <v>5</v>
@@ -12889,10 +12889,10 @@
         <v>291600</v>
       </c>
       <c r="K215" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L215" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M215" t="n">
         <v>100</v>
@@ -12916,7 +12916,7 @@
         <v>15</v>
       </c>
       <c r="E216" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F216" t="n">
         <v>5</v>
@@ -12934,10 +12934,10 @@
         <v>324000</v>
       </c>
       <c r="K216" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L216" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M216" t="n">
         <v>100</v>
@@ -12961,7 +12961,7 @@
         <v>16</v>
       </c>
       <c r="E217" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F217" t="n">
         <v>5</v>
@@ -12979,10 +12979,10 @@
         <v>367200</v>
       </c>
       <c r="K217" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L217" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M217" t="n">
         <v>100</v>
@@ -13006,7 +13006,7 @@
         <v>17</v>
       </c>
       <c r="E218" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F218" t="n">
         <v>5</v>
@@ -13024,10 +13024,10 @@
         <v>410400</v>
       </c>
       <c r="K218" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L218" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M218" t="n">
         <v>100</v>
@@ -13051,7 +13051,7 @@
         <v>18</v>
       </c>
       <c r="E219" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F219" t="n">
         <v>5</v>
@@ -13069,10 +13069,10 @@
         <v>453600</v>
       </c>
       <c r="K219" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L219" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M219" t="n">
         <v>100</v>
@@ -13096,7 +13096,7 @@
         <v>19</v>
       </c>
       <c r="E220" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F220" t="n">
         <v>5</v>
@@ -13114,10 +13114,10 @@
         <v>496800</v>
       </c>
       <c r="K220" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L220" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M220" t="n">
         <v>100</v>
@@ -13141,7 +13141,7 @@
         <v>20</v>
       </c>
       <c r="E221" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F221" t="n">
         <v>5</v>
@@ -13159,10 +13159,10 @@
         <v>540000</v>
       </c>
       <c r="K221" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L221" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M221" t="n">
         <v>100</v>
@@ -13186,7 +13186,7 @@
         <v>21</v>
       </c>
       <c r="E222" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F222" t="n">
         <v>5</v>
@@ -13204,7 +13204,7 @@
         <v>500000</v>
       </c>
       <c r="K222" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L222" t="s">
         <v>177</v>
@@ -13231,7 +13231,7 @@
         <v>22</v>
       </c>
       <c r="E223" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F223" t="n">
         <v>5</v>
@@ -13249,7 +13249,7 @@
         <v>550000</v>
       </c>
       <c r="K223" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L223" t="s">
         <v>179</v>
@@ -13276,7 +13276,7 @@
         <v>23</v>
       </c>
       <c r="E224" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F224" t="n">
         <v>5</v>
@@ -13294,7 +13294,7 @@
         <v>600000</v>
       </c>
       <c r="K224" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L224" t="s">
         <v>181</v>
@@ -13321,7 +13321,7 @@
         <v>24</v>
       </c>
       <c r="E225" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F225" t="n">
         <v>5</v>
@@ -13339,7 +13339,7 @@
         <v>650000</v>
       </c>
       <c r="K225" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L225" t="s">
         <v>183</v>
@@ -13366,7 +13366,7 @@
         <v>25</v>
       </c>
       <c r="E226" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F226" t="n">
         <v>5</v>
@@ -13384,7 +13384,7 @@
         <v>700000</v>
       </c>
       <c r="K226" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L226" t="s">
         <v>185</v>
@@ -13411,7 +13411,7 @@
         <v>26</v>
       </c>
       <c r="E227" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F227" t="n">
         <v>5</v>
@@ -13429,7 +13429,7 @@
         <v>750000</v>
       </c>
       <c r="K227" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L227" t="s">
         <v>187</v>
@@ -13456,7 +13456,7 @@
         <v>27</v>
       </c>
       <c r="E228" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F228" t="n">
         <v>5</v>
@@ -13474,7 +13474,7 @@
         <v>800000</v>
       </c>
       <c r="K228" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L228" t="s">
         <v>189</v>
@@ -13501,7 +13501,7 @@
         <v>28</v>
       </c>
       <c r="E229" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F229" t="n">
         <v>5</v>
@@ -13519,7 +13519,7 @@
         <v>850000</v>
       </c>
       <c r="K229" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L229" t="s">
         <v>191</v>
@@ -13546,7 +13546,7 @@
         <v>29</v>
       </c>
       <c r="E230" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F230" t="n">
         <v>5</v>
@@ -13564,7 +13564,7 @@
         <v>900000</v>
       </c>
       <c r="K230" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L230" t="s">
         <v>193</v>
@@ -13591,7 +13591,7 @@
         <v>30</v>
       </c>
       <c r="E231" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F231" t="n">
         <v>5</v>
@@ -13609,7 +13609,7 @@
         <v>950000</v>
       </c>
       <c r="K231" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L231" t="s">
         <v>195</v>
@@ -13636,7 +13636,7 @@
         <v>31</v>
       </c>
       <c r="E232" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F232" t="n">
         <v>5</v>
@@ -13654,7 +13654,7 @@
         <v>1000000</v>
       </c>
       <c r="K232" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L232" t="s">
         <v>197</v>
@@ -13681,7 +13681,7 @@
         <v>32</v>
       </c>
       <c r="E233" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F233" t="n">
         <v>5</v>
@@ -13699,7 +13699,7 @@
         <v>1050000</v>
       </c>
       <c r="K233" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L233" t="s">
         <v>199</v>
@@ -13726,7 +13726,7 @@
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F234" t="n">
         <v>5</v>
@@ -13744,7 +13744,7 @@
         <v>1100000</v>
       </c>
       <c r="K234" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L234" t="s">
         <v>201</v>
@@ -13771,7 +13771,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F235" t="n">
         <v>5</v>
@@ -13789,7 +13789,7 @@
         <v>1150000</v>
       </c>
       <c r="K235" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L235" t="s">
         <v>203</v>
@@ -13816,7 +13816,7 @@
         <v>35</v>
       </c>
       <c r="E236" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F236" t="n">
         <v>5</v>
@@ -13834,7 +13834,7 @@
         <v>1200000</v>
       </c>
       <c r="K236" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L236" t="s">
         <v>205</v>
@@ -13861,7 +13861,7 @@
         <v>36</v>
       </c>
       <c r="E237" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F237" t="n">
         <v>5</v>
@@ -13879,7 +13879,7 @@
         <v>1250000</v>
       </c>
       <c r="K237" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L237" t="s">
         <v>207</v>
@@ -13906,7 +13906,7 @@
         <v>37</v>
       </c>
       <c r="E238" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F238" t="n">
         <v>5</v>
@@ -13924,7 +13924,7 @@
         <v>1300000</v>
       </c>
       <c r="K238" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L238" t="s">
         <v>209</v>
@@ -13951,7 +13951,7 @@
         <v>38</v>
       </c>
       <c r="E239" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F239" t="n">
         <v>5</v>
@@ -13969,7 +13969,7 @@
         <v>1350000</v>
       </c>
       <c r="K239" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L239" t="s">
         <v>211</v>
@@ -13996,7 +13996,7 @@
         <v>39</v>
       </c>
       <c r="E240" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F240" t="n">
         <v>5</v>
@@ -14014,7 +14014,7 @@
         <v>1400000</v>
       </c>
       <c r="K240" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L240" t="s">
         <v>213</v>
@@ -14041,7 +14041,7 @@
         <v>40</v>
       </c>
       <c r="E241" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F241" t="n">
         <v>5</v>
@@ -14059,7 +14059,7 @@
         <v>1450000</v>
       </c>
       <c r="K241" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L241" t="s">
         <v>215</v>
@@ -14086,7 +14086,7 @@
         <v>41</v>
       </c>
       <c r="E242" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F242" t="n">
         <v>5</v>
@@ -14104,7 +14104,7 @@
         <v>1500000</v>
       </c>
       <c r="K242" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L242" t="s">
         <v>217</v>
@@ -14131,7 +14131,7 @@
         <v>42</v>
       </c>
       <c r="E243" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F243" t="n">
         <v>5</v>
@@ -14149,7 +14149,7 @@
         <v>1550000</v>
       </c>
       <c r="K243" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L243" t="s">
         <v>219</v>
@@ -14176,7 +14176,7 @@
         <v>43</v>
       </c>
       <c r="E244" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F244" t="n">
         <v>5</v>
@@ -14194,7 +14194,7 @@
         <v>1600000</v>
       </c>
       <c r="K244" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L244" t="s">
         <v>221</v>
@@ -14221,7 +14221,7 @@
         <v>44</v>
       </c>
       <c r="E245" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F245" t="n">
         <v>5</v>
@@ -14239,7 +14239,7 @@
         <v>1650000</v>
       </c>
       <c r="K245" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L245" t="s">
         <v>223</v>
@@ -14266,7 +14266,7 @@
         <v>45</v>
       </c>
       <c r="E246" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F246" t="n">
         <v>5</v>
@@ -14284,7 +14284,7 @@
         <v>1700000</v>
       </c>
       <c r="K246" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L246" t="s">
         <v>225</v>
@@ -14311,7 +14311,7 @@
         <v>46</v>
       </c>
       <c r="E247" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F247" t="n">
         <v>5</v>
@@ -14329,7 +14329,7 @@
         <v>1750000</v>
       </c>
       <c r="K247" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L247" t="s">
         <v>227</v>
@@ -14356,7 +14356,7 @@
         <v>47</v>
       </c>
       <c r="E248" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F248" t="n">
         <v>5</v>
@@ -14374,7 +14374,7 @@
         <v>1800000</v>
       </c>
       <c r="K248" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L248" t="s">
         <v>229</v>
@@ -14401,7 +14401,7 @@
         <v>48</v>
       </c>
       <c r="E249" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F249" t="n">
         <v>5</v>
@@ -14419,7 +14419,7 @@
         <v>1850000</v>
       </c>
       <c r="K249" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L249" t="s">
         <v>231</v>
@@ -14446,7 +14446,7 @@
         <v>49</v>
       </c>
       <c r="E250" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F250" t="n">
         <v>5</v>
@@ -14464,7 +14464,7 @@
         <v>1900000</v>
       </c>
       <c r="K250" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L250" t="s">
         <v>233</v>
@@ -14491,7 +14491,7 @@
         <v>50</v>
       </c>
       <c r="E251" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F251" t="n">
         <v>5</v>
@@ -14509,7 +14509,7 @@
         <v>1950000</v>
       </c>
       <c r="K251" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L251" t="s">
         <v>236</v>
@@ -14536,7 +14536,7 @@
         <v>51</v>
       </c>
       <c r="E252" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F252" t="n">
         <v>5</v>
@@ -14548,16 +14548,16 @@
         <v>92010010</v>
       </c>
       <c r="I252" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J252" t="n">
         <v>2000000</v>
       </c>
       <c r="K252" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L252" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M252" t="n">
         <v>100</v>
@@ -14581,7 +14581,7 @@
         <v>52</v>
       </c>
       <c r="E253" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F253" t="n">
         <v>5</v>
@@ -14593,16 +14593,16 @@
         <v>92010010</v>
       </c>
       <c r="I253" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J253" t="n">
         <v>2100000</v>
       </c>
       <c r="K253" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L253" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M253" t="n">
         <v>100</v>
@@ -14626,7 +14626,7 @@
         <v>53</v>
       </c>
       <c r="E254" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F254" t="n">
         <v>5</v>
@@ -14638,16 +14638,16 @@
         <v>92010010</v>
       </c>
       <c r="I254" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J254" t="n">
         <v>2200000</v>
       </c>
       <c r="K254" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L254" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M254" t="n">
         <v>100</v>
@@ -14671,7 +14671,7 @@
         <v>54</v>
       </c>
       <c r="E255" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F255" t="n">
         <v>5</v>
@@ -14683,16 +14683,16 @@
         <v>92010010</v>
       </c>
       <c r="I255" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J255" t="n">
         <v>2300000</v>
       </c>
       <c r="K255" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L255" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M255" t="n">
         <v>100</v>
@@ -14716,7 +14716,7 @@
         <v>55</v>
       </c>
       <c r="E256" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F256" t="n">
         <v>5</v>
@@ -14728,16 +14728,16 @@
         <v>92010010</v>
       </c>
       <c r="I256" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J256" t="n">
         <v>2400000</v>
       </c>
       <c r="K256" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L256" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M256" t="n">
         <v>100</v>
@@ -14761,7 +14761,7 @@
         <v>56</v>
       </c>
       <c r="E257" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F257" t="n">
         <v>5</v>
@@ -14773,16 +14773,16 @@
         <v>92010010</v>
       </c>
       <c r="I257" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J257" t="n">
         <v>2500000</v>
       </c>
       <c r="K257" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L257" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M257" t="n">
         <v>100</v>
@@ -14806,7 +14806,7 @@
         <v>57</v>
       </c>
       <c r="E258" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F258" t="n">
         <v>5</v>
@@ -14818,16 +14818,16 @@
         <v>92010010</v>
       </c>
       <c r="I258" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J258" t="n">
         <v>2600000</v>
       </c>
       <c r="K258" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L258" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M258" t="n">
         <v>100</v>
@@ -14851,7 +14851,7 @@
         <v>58</v>
       </c>
       <c r="E259" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F259" t="n">
         <v>5</v>
@@ -14863,16 +14863,16 @@
         <v>92010010</v>
       </c>
       <c r="I259" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J259" t="n">
         <v>2700000</v>
       </c>
       <c r="K259" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L259" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M259" t="n">
         <v>100</v>
@@ -14896,7 +14896,7 @@
         <v>59</v>
       </c>
       <c r="E260" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F260" t="n">
         <v>5</v>
@@ -14908,16 +14908,16 @@
         <v>92010010</v>
       </c>
       <c r="I260" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J260" t="n">
         <v>2800000</v>
       </c>
       <c r="K260" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L260" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M260" t="n">
         <v>100</v>
@@ -14941,7 +14941,7 @@
         <v>60</v>
       </c>
       <c r="E261" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F261" t="n">
         <v>5</v>
@@ -14953,16 +14953,16 @@
         <v>92010010</v>
       </c>
       <c r="I261" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J261" t="n">
         <v>2900000</v>
       </c>
       <c r="K261" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L261" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M261" t="n">
         <v>100</v>
@@ -14986,7 +14986,7 @@
         <v>61</v>
       </c>
       <c r="E262" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F262" t="n">
         <v>5</v>
@@ -14998,16 +14998,16 @@
         <v>92010010</v>
       </c>
       <c r="I262" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J262" t="n">
         <v>3000000</v>
       </c>
       <c r="K262" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L262" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M262" t="n">
         <v>100</v>
@@ -15031,7 +15031,7 @@
         <v>62</v>
       </c>
       <c r="E263" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F263" t="n">
         <v>5</v>
@@ -15043,16 +15043,16 @@
         <v>92010010</v>
       </c>
       <c r="I263" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J263" t="n">
         <v>3100000</v>
       </c>
       <c r="K263" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L263" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M263" t="n">
         <v>100</v>
@@ -15076,7 +15076,7 @@
         <v>63</v>
       </c>
       <c r="E264" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F264" t="n">
         <v>5</v>
@@ -15088,16 +15088,16 @@
         <v>92010010</v>
       </c>
       <c r="I264" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J264" t="n">
         <v>3200000</v>
       </c>
       <c r="K264" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L264" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M264" t="n">
         <v>100</v>
@@ -15121,7 +15121,7 @@
         <v>64</v>
       </c>
       <c r="E265" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F265" t="n">
         <v>5</v>
@@ -15133,16 +15133,16 @@
         <v>92010010</v>
       </c>
       <c r="I265" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J265" t="n">
         <v>3300000</v>
       </c>
       <c r="K265" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L265" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M265" t="n">
         <v>100</v>
@@ -15166,7 +15166,7 @@
         <v>65</v>
       </c>
       <c r="E266" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F266" t="n">
         <v>5</v>
@@ -15178,16 +15178,16 @@
         <v>92010010</v>
       </c>
       <c r="I266" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J266" t="n">
         <v>3400000</v>
       </c>
       <c r="K266" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L266" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M266" t="n">
         <v>100</v>
@@ -15211,7 +15211,7 @@
         <v>66</v>
       </c>
       <c r="E267" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F267" t="n">
         <v>5</v>
@@ -15223,16 +15223,16 @@
         <v>92010010</v>
       </c>
       <c r="I267" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J267" t="n">
         <v>3500000</v>
       </c>
       <c r="K267" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L267" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M267" t="n">
         <v>100</v>
@@ -15256,7 +15256,7 @@
         <v>67</v>
       </c>
       <c r="E268" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F268" t="n">
         <v>5</v>
@@ -15268,16 +15268,16 @@
         <v>92010010</v>
       </c>
       <c r="I268" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J268" t="n">
         <v>3600000</v>
       </c>
       <c r="K268" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L268" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M268" t="n">
         <v>100</v>
@@ -15301,7 +15301,7 @@
         <v>68</v>
       </c>
       <c r="E269" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F269" t="n">
         <v>5</v>
@@ -15313,16 +15313,16 @@
         <v>92010010</v>
       </c>
       <c r="I269" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J269" t="n">
         <v>3700000</v>
       </c>
       <c r="K269" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L269" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M269" t="n">
         <v>100</v>
@@ -15346,7 +15346,7 @@
         <v>69</v>
       </c>
       <c r="E270" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F270" t="n">
         <v>5</v>
@@ -15358,16 +15358,16 @@
         <v>92010010</v>
       </c>
       <c r="I270" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J270" t="n">
         <v>3800000</v>
       </c>
       <c r="K270" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L270" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M270" t="n">
         <v>100</v>
@@ -15391,7 +15391,7 @@
         <v>70</v>
       </c>
       <c r="E271" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F271" t="n">
         <v>5</v>
@@ -15403,16 +15403,16 @@
         <v>92010010</v>
       </c>
       <c r="I271" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J271" t="n">
         <v>3900000</v>
       </c>
       <c r="K271" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L271" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M271" t="n">
         <v>100</v>
@@ -15436,7 +15436,7 @@
         <v>71</v>
       </c>
       <c r="E272" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F272" t="n">
         <v>5</v>
@@ -15448,16 +15448,16 @@
         <v>92010010</v>
       </c>
       <c r="I272" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J272" t="n">
         <v>4000000</v>
       </c>
       <c r="K272" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L272" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M272" t="n">
         <v>100</v>
@@ -15480,7 +15480,7 @@
         <v>72</v>
       </c>
       <c r="E273" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F273" t="n">
         <v>5</v>
@@ -15492,16 +15492,16 @@
         <v>92010010</v>
       </c>
       <c r="I273" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J273" t="n">
         <v>4100000</v>
       </c>
       <c r="K273" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L273" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M273" t="n">
         <v>100</v>
@@ -15524,7 +15524,7 @@
         <v>73</v>
       </c>
       <c r="E274" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F274" t="n">
         <v>5</v>
@@ -15536,16 +15536,16 @@
         <v>92010010</v>
       </c>
       <c r="I274" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J274" t="n">
         <v>4200000</v>
       </c>
       <c r="K274" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L274" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M274" t="n">
         <v>100</v>
@@ -15568,7 +15568,7 @@
         <v>74</v>
       </c>
       <c r="E275" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F275" t="n">
         <v>5</v>
@@ -15580,16 +15580,16 @@
         <v>92010010</v>
       </c>
       <c r="I275" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J275" t="n">
         <v>4300000</v>
       </c>
       <c r="K275" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L275" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M275" t="n">
         <v>100</v>
@@ -15612,7 +15612,7 @@
         <v>75</v>
       </c>
       <c r="E276" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F276" t="n">
         <v>5</v>
@@ -15624,16 +15624,16 @@
         <v>92010010</v>
       </c>
       <c r="I276" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J276" t="n">
         <v>4400000</v>
       </c>
       <c r="K276" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L276" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M276" t="n">
         <v>100</v>
@@ -15656,7 +15656,7 @@
         <v>76</v>
       </c>
       <c r="E277" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F277" t="n">
         <v>5</v>
@@ -15668,16 +15668,16 @@
         <v>92010010</v>
       </c>
       <c r="I277" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J277" t="n">
         <v>4500000</v>
       </c>
       <c r="K277" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L277" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M277" t="n">
         <v>100</v>
@@ -15700,7 +15700,7 @@
         <v>77</v>
       </c>
       <c r="E278" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F278" t="n">
         <v>5</v>
@@ -15712,16 +15712,16 @@
         <v>92010010</v>
       </c>
       <c r="I278" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J278" t="n">
         <v>4600000</v>
       </c>
       <c r="K278" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L278" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M278" t="n">
         <v>100</v>
@@ -15744,7 +15744,7 @@
         <v>78</v>
       </c>
       <c r="E279" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F279" t="n">
         <v>5</v>
@@ -15756,16 +15756,16 @@
         <v>92010010</v>
       </c>
       <c r="I279" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J279" t="n">
         <v>4700000</v>
       </c>
       <c r="K279" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L279" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M279" t="n">
         <v>100</v>
@@ -15788,7 +15788,7 @@
         <v>79</v>
       </c>
       <c r="E280" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F280" t="n">
         <v>5</v>
@@ -15800,16 +15800,16 @@
         <v>92010010</v>
       </c>
       <c r="I280" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J280" t="n">
         <v>4800000</v>
       </c>
       <c r="K280" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L280" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M280" t="n">
         <v>100</v>
@@ -15832,7 +15832,7 @@
         <v>80</v>
       </c>
       <c r="E281" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F281" t="n">
         <v>5</v>
@@ -15844,7 +15844,7 @@
         <v>92010010</v>
       </c>
       <c r="I281" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J281" t="n">
         <v>4900000</v>
@@ -15853,7 +15853,7 @@
         <v>0</v>
       </c>
       <c r="L281" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M281" t="n">
         <v>0</v>
@@ -15876,7 +15876,7 @@
         <v>1</v>
       </c>
       <c r="E282" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F282" t="n">
         <v>2</v>
@@ -15894,10 +15894,10 @@
         <v>1950</v>
       </c>
       <c r="K282" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L282" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M282" t="n">
         <v>100</v>
@@ -15920,7 +15920,7 @@
         <v>2</v>
       </c>
       <c r="E283" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F283" t="n">
         <v>2</v>
@@ -15938,10 +15938,10 @@
         <v>3900</v>
       </c>
       <c r="K283" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L283" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M283" t="n">
         <v>100</v>
@@ -15964,7 +15964,7 @@
         <v>3</v>
       </c>
       <c r="E284" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F284" t="n">
         <v>2</v>
@@ -15982,10 +15982,10 @@
         <v>5850</v>
       </c>
       <c r="K284" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L284" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M284" t="n">
         <v>100</v>
@@ -16008,7 +16008,7 @@
         <v>4</v>
       </c>
       <c r="E285" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F285" t="n">
         <v>2</v>
@@ -16026,10 +16026,10 @@
         <v>7800</v>
       </c>
       <c r="K285" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L285" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M285" t="n">
         <v>100</v>
@@ -16052,7 +16052,7 @@
         <v>5</v>
       </c>
       <c r="E286" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F286" t="n">
         <v>2</v>
@@ -16070,10 +16070,10 @@
         <v>9750</v>
       </c>
       <c r="K286" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L286" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M286" t="n">
         <v>100</v>
@@ -16096,7 +16096,7 @@
         <v>6</v>
       </c>
       <c r="E287" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F287" t="n">
         <v>2</v>
@@ -16114,10 +16114,10 @@
         <v>13650</v>
       </c>
       <c r="K287" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L287" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M287" t="n">
         <v>100</v>
@@ -16140,7 +16140,7 @@
         <v>7</v>
       </c>
       <c r="E288" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F288" t="n">
         <v>2</v>
@@ -16158,10 +16158,10 @@
         <v>17550</v>
       </c>
       <c r="K288" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L288" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M288" t="n">
         <v>100</v>
@@ -16184,7 +16184,7 @@
         <v>8</v>
       </c>
       <c r="E289" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F289" t="n">
         <v>2</v>
@@ -16202,10 +16202,10 @@
         <v>21450</v>
       </c>
       <c r="K289" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L289" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M289" t="n">
         <v>100</v>
@@ -16228,7 +16228,7 @@
         <v>9</v>
       </c>
       <c r="E290" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F290" t="n">
         <v>2</v>
@@ -16246,10 +16246,10 @@
         <v>25350</v>
       </c>
       <c r="K290" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L290" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M290" t="n">
         <v>100</v>
@@ -16272,7 +16272,7 @@
         <v>10</v>
       </c>
       <c r="E291" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F291" t="n">
         <v>2</v>
@@ -16290,10 +16290,10 @@
         <v>29250</v>
       </c>
       <c r="K291" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L291" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M291" t="n">
         <v>100</v>
@@ -16316,7 +16316,7 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F292" t="n">
         <v>2</v>
@@ -16334,10 +16334,10 @@
         <v>35100</v>
       </c>
       <c r="K292" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L292" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M292" t="n">
         <v>100</v>
@@ -16360,7 +16360,7 @@
         <v>12</v>
       </c>
       <c r="E293" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F293" t="n">
         <v>2</v>
@@ -16378,10 +16378,10 @@
         <v>40950</v>
       </c>
       <c r="K293" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L293" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M293" t="n">
         <v>100</v>
@@ -16404,7 +16404,7 @@
         <v>13</v>
       </c>
       <c r="E294" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F294" t="n">
         <v>2</v>
@@ -16422,10 +16422,10 @@
         <v>46800</v>
       </c>
       <c r="K294" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L294" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M294" t="n">
         <v>100</v>
@@ -16448,7 +16448,7 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F295" t="n">
         <v>2</v>
@@ -16466,10 +16466,10 @@
         <v>52650</v>
       </c>
       <c r="K295" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L295" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M295" t="n">
         <v>100</v>
@@ -16492,7 +16492,7 @@
         <v>15</v>
       </c>
       <c r="E296" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F296" t="n">
         <v>2</v>
@@ -16510,10 +16510,10 @@
         <v>58500</v>
       </c>
       <c r="K296" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L296" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M296" t="n">
         <v>100</v>
@@ -16536,7 +16536,7 @@
         <v>16</v>
       </c>
       <c r="E297" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F297" t="n">
         <v>2</v>
@@ -16554,10 +16554,10 @@
         <v>66300</v>
       </c>
       <c r="K297" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L297" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M297" t="n">
         <v>100</v>
@@ -16580,7 +16580,7 @@
         <v>17</v>
       </c>
       <c r="E298" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F298" t="n">
         <v>2</v>
@@ -16598,10 +16598,10 @@
         <v>74100</v>
       </c>
       <c r="K298" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L298" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M298" t="n">
         <v>100</v>
@@ -16624,7 +16624,7 @@
         <v>18</v>
       </c>
       <c r="E299" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F299" t="n">
         <v>2</v>
@@ -16642,10 +16642,10 @@
         <v>81900</v>
       </c>
       <c r="K299" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L299" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M299" t="n">
         <v>100</v>
@@ -16668,7 +16668,7 @@
         <v>19</v>
       </c>
       <c r="E300" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F300" t="n">
         <v>2</v>
@@ -16686,10 +16686,10 @@
         <v>89700</v>
       </c>
       <c r="K300" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L300" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M300" t="n">
         <v>100</v>
@@ -16712,7 +16712,7 @@
         <v>20</v>
       </c>
       <c r="E301" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F301" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>98</v>
       </c>
       <c r="L301" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M301" t="n">
         <v>0</v>
@@ -16756,7 +16756,7 @@
         <v>1</v>
       </c>
       <c r="E302" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F302" t="n">
         <v>3</v>
@@ -16774,10 +16774,10 @@
         <v>3900</v>
       </c>
       <c r="K302" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L302" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M302" t="n">
         <v>100</v>
@@ -16800,7 +16800,7 @@
         <v>2</v>
       </c>
       <c r="E303" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F303" t="n">
         <v>3</v>
@@ -16818,10 +16818,10 @@
         <v>7800</v>
       </c>
       <c r="K303" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L303" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M303" t="n">
         <v>100</v>
@@ -16844,7 +16844,7 @@
         <v>3</v>
       </c>
       <c r="E304" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F304" t="n">
         <v>3</v>
@@ -16862,10 +16862,10 @@
         <v>11700</v>
       </c>
       <c r="K304" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L304" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M304" t="n">
         <v>100</v>
@@ -16888,7 +16888,7 @@
         <v>4</v>
       </c>
       <c r="E305" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F305" t="n">
         <v>3</v>
@@ -16906,10 +16906,10 @@
         <v>15600</v>
       </c>
       <c r="K305" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L305" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M305" t="n">
         <v>100</v>
@@ -16932,7 +16932,7 @@
         <v>5</v>
       </c>
       <c r="E306" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F306" t="n">
         <v>3</v>
@@ -16950,10 +16950,10 @@
         <v>19500</v>
       </c>
       <c r="K306" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L306" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M306" t="n">
         <v>100</v>
@@ -16976,7 +16976,7 @@
         <v>6</v>
       </c>
       <c r="E307" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F307" t="n">
         <v>3</v>
@@ -16994,10 +16994,10 @@
         <v>27300</v>
       </c>
       <c r="K307" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L307" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M307" t="n">
         <v>100</v>
@@ -17020,7 +17020,7 @@
         <v>7</v>
       </c>
       <c r="E308" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F308" t="n">
         <v>3</v>
@@ -17038,10 +17038,10 @@
         <v>35100</v>
       </c>
       <c r="K308" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L308" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M308" t="n">
         <v>100</v>
@@ -17064,7 +17064,7 @@
         <v>8</v>
       </c>
       <c r="E309" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F309" t="n">
         <v>3</v>
@@ -17082,10 +17082,10 @@
         <v>42900</v>
       </c>
       <c r="K309" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L309" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M309" t="n">
         <v>100</v>
@@ -17108,7 +17108,7 @@
         <v>9</v>
       </c>
       <c r="E310" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F310" t="n">
         <v>3</v>
@@ -17126,10 +17126,10 @@
         <v>50700</v>
       </c>
       <c r="K310" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L310" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M310" t="n">
         <v>100</v>
@@ -17152,7 +17152,7 @@
         <v>10</v>
       </c>
       <c r="E311" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F311" t="n">
         <v>3</v>
@@ -17170,10 +17170,10 @@
         <v>58500</v>
       </c>
       <c r="K311" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L311" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M311" t="n">
         <v>100</v>
@@ -17196,7 +17196,7 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F312" t="n">
         <v>3</v>
@@ -17214,10 +17214,10 @@
         <v>70200</v>
       </c>
       <c r="K312" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L312" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M312" t="n">
         <v>100</v>
@@ -17240,7 +17240,7 @@
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F313" t="n">
         <v>3</v>
@@ -17258,10 +17258,10 @@
         <v>81900</v>
       </c>
       <c r="K313" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L313" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M313" t="n">
         <v>100</v>
@@ -17284,7 +17284,7 @@
         <v>13</v>
       </c>
       <c r="E314" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F314" t="n">
         <v>3</v>
@@ -17302,10 +17302,10 @@
         <v>93600</v>
       </c>
       <c r="K314" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L314" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M314" t="n">
         <v>100</v>
@@ -17328,7 +17328,7 @@
         <v>14</v>
       </c>
       <c r="E315" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F315" t="n">
         <v>3</v>
@@ -17346,10 +17346,10 @@
         <v>105300</v>
       </c>
       <c r="K315" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L315" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M315" t="n">
         <v>100</v>
@@ -17372,7 +17372,7 @@
         <v>15</v>
       </c>
       <c r="E316" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F316" t="n">
         <v>3</v>
@@ -17390,10 +17390,10 @@
         <v>117000</v>
       </c>
       <c r="K316" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L316" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M316" t="n">
         <v>100</v>
@@ -17416,7 +17416,7 @@
         <v>16</v>
       </c>
       <c r="E317" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F317" t="n">
         <v>3</v>
@@ -17434,10 +17434,10 @@
         <v>132600</v>
       </c>
       <c r="K317" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L317" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M317" t="n">
         <v>100</v>
@@ -17460,7 +17460,7 @@
         <v>17</v>
       </c>
       <c r="E318" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F318" t="n">
         <v>3</v>
@@ -17478,10 +17478,10 @@
         <v>148200</v>
       </c>
       <c r="K318" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L318" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M318" t="n">
         <v>100</v>
@@ -17504,7 +17504,7 @@
         <v>18</v>
       </c>
       <c r="E319" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F319" t="n">
         <v>3</v>
@@ -17522,10 +17522,10 @@
         <v>163800</v>
       </c>
       <c r="K319" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L319" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M319" t="n">
         <v>100</v>
@@ -17548,7 +17548,7 @@
         <v>19</v>
       </c>
       <c r="E320" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F320" t="n">
         <v>3</v>
@@ -17566,10 +17566,10 @@
         <v>179400</v>
       </c>
       <c r="K320" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L320" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M320" t="n">
         <v>100</v>
@@ -17592,7 +17592,7 @@
         <v>20</v>
       </c>
       <c r="E321" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F321" t="n">
         <v>3</v>
@@ -17613,7 +17613,7 @@
         <v>98</v>
       </c>
       <c r="L321" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M321" t="n">
         <v>0</v>
@@ -17636,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="E322" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F322" t="n">
         <v>4</v>
@@ -17654,10 +17654,10 @@
         <v>5850</v>
       </c>
       <c r="K322" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L322" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M322" t="n">
         <v>100</v>
@@ -17680,7 +17680,7 @@
         <v>2</v>
       </c>
       <c r="E323" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F323" t="n">
         <v>4</v>
@@ -17698,10 +17698,10 @@
         <v>11700</v>
       </c>
       <c r="K323" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L323" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M323" t="n">
         <v>100</v>
@@ -17724,7 +17724,7 @@
         <v>3</v>
       </c>
       <c r="E324" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F324" t="n">
         <v>4</v>
@@ -17742,10 +17742,10 @@
         <v>17550</v>
       </c>
       <c r="K324" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L324" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M324" t="n">
         <v>100</v>
@@ -17768,7 +17768,7 @@
         <v>4</v>
       </c>
       <c r="E325" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F325" t="n">
         <v>4</v>
@@ -17786,10 +17786,10 @@
         <v>23400</v>
       </c>
       <c r="K325" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L325" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M325" t="n">
         <v>100</v>
@@ -17812,7 +17812,7 @@
         <v>5</v>
       </c>
       <c r="E326" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F326" t="n">
         <v>4</v>
@@ -17830,10 +17830,10 @@
         <v>29250</v>
       </c>
       <c r="K326" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L326" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M326" t="n">
         <v>100</v>
@@ -17856,7 +17856,7 @@
         <v>6</v>
       </c>
       <c r="E327" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F327" t="n">
         <v>4</v>
@@ -17874,10 +17874,10 @@
         <v>40950</v>
       </c>
       <c r="K327" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L327" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M327" t="n">
         <v>100</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="E328" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F328" t="n">
         <v>4</v>
@@ -17918,10 +17918,10 @@
         <v>52650</v>
       </c>
       <c r="K328" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L328" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M328" t="n">
         <v>100</v>
@@ -17944,7 +17944,7 @@
         <v>8</v>
       </c>
       <c r="E329" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F329" t="n">
         <v>4</v>
@@ -17962,10 +17962,10 @@
         <v>64350</v>
       </c>
       <c r="K329" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L329" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M329" t="n">
         <v>100</v>
@@ -17988,7 +17988,7 @@
         <v>9</v>
       </c>
       <c r="E330" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F330" t="n">
         <v>4</v>
@@ -18006,10 +18006,10 @@
         <v>76050</v>
       </c>
       <c r="K330" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L330" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M330" t="n">
         <v>100</v>
@@ -18032,7 +18032,7 @@
         <v>10</v>
       </c>
       <c r="E331" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F331" t="n">
         <v>4</v>
@@ -18050,10 +18050,10 @@
         <v>87750</v>
       </c>
       <c r="K331" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L331" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M331" t="n">
         <v>100</v>
@@ -18076,7 +18076,7 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F332" t="n">
         <v>4</v>
@@ -18094,10 +18094,10 @@
         <v>105300</v>
       </c>
       <c r="K332" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L332" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M332" t="n">
         <v>100</v>
@@ -18120,7 +18120,7 @@
         <v>12</v>
       </c>
       <c r="E333" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F333" t="n">
         <v>4</v>
@@ -18138,10 +18138,10 @@
         <v>122850</v>
       </c>
       <c r="K333" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L333" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M333" t="n">
         <v>100</v>
@@ -18164,7 +18164,7 @@
         <v>13</v>
       </c>
       <c r="E334" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F334" t="n">
         <v>4</v>
@@ -18182,10 +18182,10 @@
         <v>140400</v>
       </c>
       <c r="K334" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L334" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M334" t="n">
         <v>100</v>
@@ -18208,7 +18208,7 @@
         <v>14</v>
       </c>
       <c r="E335" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F335" t="n">
         <v>4</v>
@@ -18226,10 +18226,10 @@
         <v>157950</v>
       </c>
       <c r="K335" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L335" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M335" t="n">
         <v>100</v>
@@ -18252,7 +18252,7 @@
         <v>15</v>
       </c>
       <c r="E336" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F336" t="n">
         <v>4</v>
@@ -18270,10 +18270,10 @@
         <v>175500</v>
       </c>
       <c r="K336" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L336" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M336" t="n">
         <v>100</v>
@@ -18296,7 +18296,7 @@
         <v>16</v>
       </c>
       <c r="E337" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F337" t="n">
         <v>4</v>
@@ -18314,10 +18314,10 @@
         <v>198900</v>
       </c>
       <c r="K337" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L337" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M337" t="n">
         <v>100</v>
@@ -18340,7 +18340,7 @@
         <v>17</v>
       </c>
       <c r="E338" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F338" t="n">
         <v>4</v>
@@ -18358,10 +18358,10 @@
         <v>222300</v>
       </c>
       <c r="K338" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L338" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M338" t="n">
         <v>100</v>
@@ -18384,7 +18384,7 @@
         <v>18</v>
       </c>
       <c r="E339" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F339" t="n">
         <v>4</v>
@@ -18402,10 +18402,10 @@
         <v>245700</v>
       </c>
       <c r="K339" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L339" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M339" t="n">
         <v>100</v>
@@ -18428,7 +18428,7 @@
         <v>19</v>
       </c>
       <c r="E340" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F340" t="n">
         <v>4</v>
@@ -18446,10 +18446,10 @@
         <v>269100</v>
       </c>
       <c r="K340" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L340" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M340" t="n">
         <v>100</v>
@@ -18472,7 +18472,7 @@
         <v>20</v>
       </c>
       <c r="E341" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F341" t="n">
         <v>4</v>
@@ -18493,7 +18493,7 @@
         <v>98</v>
       </c>
       <c r="L341" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M341" t="n">
         <v>0</v>
@@ -18516,7 +18516,7 @@
         <v>1</v>
       </c>
       <c r="E342" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F342" t="n">
         <v>5</v>
@@ -18534,10 +18534,10 @@
         <v>7800</v>
       </c>
       <c r="K342" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L342" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M342" t="n">
         <v>100</v>
@@ -18560,7 +18560,7 @@
         <v>2</v>
       </c>
       <c r="E343" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F343" t="n">
         <v>5</v>
@@ -18578,10 +18578,10 @@
         <v>15600</v>
       </c>
       <c r="K343" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L343" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M343" t="n">
         <v>100</v>
@@ -18604,7 +18604,7 @@
         <v>3</v>
       </c>
       <c r="E344" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F344" t="n">
         <v>5</v>
@@ -18622,10 +18622,10 @@
         <v>23400</v>
       </c>
       <c r="K344" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L344" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M344" t="n">
         <v>100</v>
@@ -18648,7 +18648,7 @@
         <v>4</v>
       </c>
       <c r="E345" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F345" t="n">
         <v>5</v>
@@ -18666,10 +18666,10 @@
         <v>31200</v>
       </c>
       <c r="K345" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L345" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M345" t="n">
         <v>100</v>
@@ -18692,7 +18692,7 @@
         <v>5</v>
       </c>
       <c r="E346" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F346" t="n">
         <v>5</v>
@@ -18710,10 +18710,10 @@
         <v>39000</v>
       </c>
       <c r="K346" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L346" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M346" t="n">
         <v>100</v>
@@ -18736,7 +18736,7 @@
         <v>6</v>
       </c>
       <c r="E347" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F347" t="n">
         <v>5</v>
@@ -18754,10 +18754,10 @@
         <v>54600</v>
       </c>
       <c r="K347" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L347" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M347" t="n">
         <v>100</v>
@@ -18780,7 +18780,7 @@
         <v>7</v>
       </c>
       <c r="E348" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F348" t="n">
         <v>5</v>
@@ -18798,10 +18798,10 @@
         <v>70200</v>
       </c>
       <c r="K348" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L348" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M348" t="n">
         <v>100</v>
@@ -18824,7 +18824,7 @@
         <v>8</v>
       </c>
       <c r="E349" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F349" t="n">
         <v>5</v>
@@ -18842,10 +18842,10 @@
         <v>85800</v>
       </c>
       <c r="K349" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L349" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M349" t="n">
         <v>100</v>
@@ -18868,7 +18868,7 @@
         <v>9</v>
       </c>
       <c r="E350" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F350" t="n">
         <v>5</v>
@@ -18886,10 +18886,10 @@
         <v>101400</v>
       </c>
       <c r="K350" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L350" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M350" t="n">
         <v>100</v>
@@ -18912,7 +18912,7 @@
         <v>10</v>
       </c>
       <c r="E351" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F351" t="n">
         <v>5</v>
@@ -18930,10 +18930,10 @@
         <v>117000</v>
       </c>
       <c r="K351" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L351" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M351" t="n">
         <v>100</v>
@@ -18956,7 +18956,7 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F352" t="n">
         <v>5</v>
@@ -18974,10 +18974,10 @@
         <v>140400</v>
       </c>
       <c r="K352" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L352" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M352" t="n">
         <v>100</v>
@@ -19000,7 +19000,7 @@
         <v>12</v>
       </c>
       <c r="E353" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F353" t="n">
         <v>5</v>
@@ -19018,10 +19018,10 @@
         <v>163800</v>
       </c>
       <c r="K353" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L353" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M353" t="n">
         <v>100</v>
@@ -19044,7 +19044,7 @@
         <v>13</v>
       </c>
       <c r="E354" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F354" t="n">
         <v>5</v>
@@ -19062,10 +19062,10 @@
         <v>187200</v>
       </c>
       <c r="K354" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L354" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M354" t="n">
         <v>100</v>
@@ -19088,7 +19088,7 @@
         <v>14</v>
       </c>
       <c r="E355" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F355" t="n">
         <v>5</v>
@@ -19106,10 +19106,10 @@
         <v>210600</v>
       </c>
       <c r="K355" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L355" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M355" t="n">
         <v>100</v>
@@ -19132,7 +19132,7 @@
         <v>15</v>
       </c>
       <c r="E356" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F356" t="n">
         <v>5</v>
@@ -19150,10 +19150,10 @@
         <v>234000</v>
       </c>
       <c r="K356" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L356" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M356" t="n">
         <v>100</v>
@@ -19176,7 +19176,7 @@
         <v>16</v>
       </c>
       <c r="E357" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F357" t="n">
         <v>5</v>
@@ -19194,10 +19194,10 @@
         <v>265200</v>
       </c>
       <c r="K357" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L357" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M357" t="n">
         <v>100</v>
@@ -19220,7 +19220,7 @@
         <v>17</v>
       </c>
       <c r="E358" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F358" t="n">
         <v>5</v>
@@ -19238,10 +19238,10 @@
         <v>296400</v>
       </c>
       <c r="K358" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L358" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M358" t="n">
         <v>100</v>
@@ -19264,7 +19264,7 @@
         <v>18</v>
       </c>
       <c r="E359" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F359" t="n">
         <v>5</v>
@@ -19282,10 +19282,10 @@
         <v>327600</v>
       </c>
       <c r="K359" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L359" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M359" t="n">
         <v>100</v>
@@ -19308,7 +19308,7 @@
         <v>19</v>
       </c>
       <c r="E360" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F360" t="n">
         <v>5</v>
@@ -19326,10 +19326,10 @@
         <v>358800</v>
       </c>
       <c r="K360" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L360" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M360" t="n">
         <v>100</v>
@@ -19352,7 +19352,7 @@
         <v>20</v>
       </c>
       <c r="E361" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F361" t="n">
         <v>5</v>
@@ -19370,10 +19370,10 @@
         <v>390000</v>
       </c>
       <c r="K361" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L361" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M361" t="n">
         <v>100</v>
@@ -19396,7 +19396,7 @@
         <v>21</v>
       </c>
       <c r="E362" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F362" t="n">
         <v>5</v>
@@ -19414,7 +19414,7 @@
         <v>500000</v>
       </c>
       <c r="K362" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L362" t="s">
         <v>177</v>
@@ -19440,7 +19440,7 @@
         <v>22</v>
       </c>
       <c r="E363" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F363" t="n">
         <v>5</v>
@@ -19458,7 +19458,7 @@
         <v>550000</v>
       </c>
       <c r="K363" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L363" t="s">
         <v>179</v>
@@ -19484,7 +19484,7 @@
         <v>23</v>
       </c>
       <c r="E364" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F364" t="n">
         <v>5</v>
@@ -19502,7 +19502,7 @@
         <v>600000</v>
       </c>
       <c r="K364" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L364" t="s">
         <v>181</v>
@@ -19528,7 +19528,7 @@
         <v>24</v>
       </c>
       <c r="E365" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F365" t="n">
         <v>5</v>
@@ -19546,7 +19546,7 @@
         <v>650000</v>
       </c>
       <c r="K365" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L365" t="s">
         <v>183</v>
@@ -19572,7 +19572,7 @@
         <v>25</v>
       </c>
       <c r="E366" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F366" t="n">
         <v>5</v>
@@ -19590,7 +19590,7 @@
         <v>700000</v>
       </c>
       <c r="K366" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L366" t="s">
         <v>185</v>
@@ -19616,7 +19616,7 @@
         <v>26</v>
       </c>
       <c r="E367" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F367" t="n">
         <v>5</v>
@@ -19634,7 +19634,7 @@
         <v>750000</v>
       </c>
       <c r="K367" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L367" t="s">
         <v>187</v>
@@ -19660,7 +19660,7 @@
         <v>27</v>
       </c>
       <c r="E368" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F368" t="n">
         <v>5</v>
@@ -19678,7 +19678,7 @@
         <v>800000</v>
       </c>
       <c r="K368" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L368" t="s">
         <v>189</v>
@@ -19704,7 +19704,7 @@
         <v>28</v>
       </c>
       <c r="E369" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F369" t="n">
         <v>5</v>
@@ -19722,7 +19722,7 @@
         <v>850000</v>
       </c>
       <c r="K369" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L369" t="s">
         <v>191</v>
@@ -19748,7 +19748,7 @@
         <v>29</v>
       </c>
       <c r="E370" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F370" t="n">
         <v>5</v>
@@ -19766,7 +19766,7 @@
         <v>900000</v>
       </c>
       <c r="K370" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L370" t="s">
         <v>193</v>
@@ -19792,7 +19792,7 @@
         <v>30</v>
       </c>
       <c r="E371" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F371" t="n">
         <v>5</v>
@@ -19810,7 +19810,7 @@
         <v>950000</v>
       </c>
       <c r="K371" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L371" t="s">
         <v>195</v>
@@ -19836,7 +19836,7 @@
         <v>31</v>
       </c>
       <c r="E372" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F372" t="n">
         <v>5</v>
@@ -19854,7 +19854,7 @@
         <v>1000000</v>
       </c>
       <c r="K372" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L372" t="s">
         <v>197</v>
@@ -19880,7 +19880,7 @@
         <v>32</v>
       </c>
       <c r="E373" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F373" t="n">
         <v>5</v>
@@ -19898,7 +19898,7 @@
         <v>1050000</v>
       </c>
       <c r="K373" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L373" t="s">
         <v>199</v>
@@ -19924,7 +19924,7 @@
         <v>33</v>
       </c>
       <c r="E374" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F374" t="n">
         <v>5</v>
@@ -19942,7 +19942,7 @@
         <v>1100000</v>
       </c>
       <c r="K374" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L374" t="s">
         <v>201</v>
@@ -19968,7 +19968,7 @@
         <v>34</v>
       </c>
       <c r="E375" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F375" t="n">
         <v>5</v>
@@ -19986,7 +19986,7 @@
         <v>1150000</v>
       </c>
       <c r="K375" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L375" t="s">
         <v>203</v>
@@ -20012,7 +20012,7 @@
         <v>35</v>
       </c>
       <c r="E376" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F376" t="n">
         <v>5</v>
@@ -20030,7 +20030,7 @@
         <v>1200000</v>
       </c>
       <c r="K376" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L376" t="s">
         <v>205</v>
@@ -20056,7 +20056,7 @@
         <v>36</v>
       </c>
       <c r="E377" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F377" t="n">
         <v>5</v>
@@ -20074,7 +20074,7 @@
         <v>1250000</v>
       </c>
       <c r="K377" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L377" t="s">
         <v>207</v>
@@ -20100,7 +20100,7 @@
         <v>37</v>
       </c>
       <c r="E378" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F378" t="n">
         <v>5</v>
@@ -20118,7 +20118,7 @@
         <v>1300000</v>
       </c>
       <c r="K378" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L378" t="s">
         <v>209</v>
@@ -20144,7 +20144,7 @@
         <v>38</v>
       </c>
       <c r="E379" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F379" t="n">
         <v>5</v>
@@ -20162,7 +20162,7 @@
         <v>1350000</v>
       </c>
       <c r="K379" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L379" t="s">
         <v>211</v>
@@ -20188,7 +20188,7 @@
         <v>39</v>
       </c>
       <c r="E380" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F380" t="n">
         <v>5</v>
@@ -20206,7 +20206,7 @@
         <v>1400000</v>
       </c>
       <c r="K380" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L380" t="s">
         <v>213</v>
@@ -20232,7 +20232,7 @@
         <v>40</v>
       </c>
       <c r="E381" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F381" t="n">
         <v>5</v>
@@ -20250,7 +20250,7 @@
         <v>1450000</v>
       </c>
       <c r="K381" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L381" t="s">
         <v>215</v>
@@ -20276,7 +20276,7 @@
         <v>41</v>
       </c>
       <c r="E382" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F382" t="n">
         <v>5</v>
@@ -20294,7 +20294,7 @@
         <v>1500000</v>
       </c>
       <c r="K382" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L382" t="s">
         <v>217</v>
@@ -20320,7 +20320,7 @@
         <v>42</v>
       </c>
       <c r="E383" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F383" t="n">
         <v>5</v>
@@ -20338,7 +20338,7 @@
         <v>1550000</v>
       </c>
       <c r="K383" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L383" t="s">
         <v>219</v>
@@ -20364,7 +20364,7 @@
         <v>43</v>
       </c>
       <c r="E384" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F384" t="n">
         <v>5</v>
@@ -20382,7 +20382,7 @@
         <v>1600000</v>
       </c>
       <c r="K384" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L384" t="s">
         <v>221</v>
@@ -20408,7 +20408,7 @@
         <v>44</v>
       </c>
       <c r="E385" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F385" t="n">
         <v>5</v>
@@ -20426,7 +20426,7 @@
         <v>1650000</v>
       </c>
       <c r="K385" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L385" t="s">
         <v>223</v>
@@ -20452,7 +20452,7 @@
         <v>45</v>
       </c>
       <c r="E386" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F386" t="n">
         <v>5</v>
@@ -20470,7 +20470,7 @@
         <v>1700000</v>
       </c>
       <c r="K386" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L386" t="s">
         <v>225</v>
@@ -20496,7 +20496,7 @@
         <v>46</v>
       </c>
       <c r="E387" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F387" t="n">
         <v>5</v>
@@ -20514,7 +20514,7 @@
         <v>1750000</v>
       </c>
       <c r="K387" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L387" t="s">
         <v>227</v>
@@ -20540,7 +20540,7 @@
         <v>47</v>
       </c>
       <c r="E388" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F388" t="n">
         <v>5</v>
@@ -20558,7 +20558,7 @@
         <v>1800000</v>
       </c>
       <c r="K388" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L388" t="s">
         <v>229</v>
@@ -20584,7 +20584,7 @@
         <v>48</v>
       </c>
       <c r="E389" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F389" t="n">
         <v>5</v>
@@ -20602,7 +20602,7 @@
         <v>1850000</v>
       </c>
       <c r="K389" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L389" t="s">
         <v>231</v>
@@ -20628,7 +20628,7 @@
         <v>49</v>
       </c>
       <c r="E390" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F390" t="n">
         <v>5</v>
@@ -20646,7 +20646,7 @@
         <v>1900000</v>
       </c>
       <c r="K390" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L390" t="s">
         <v>233</v>
@@ -20672,7 +20672,7 @@
         <v>50</v>
       </c>
       <c r="E391" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F391" t="n">
         <v>5</v>
@@ -20690,7 +20690,7 @@
         <v>1950000</v>
       </c>
       <c r="K391" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L391" t="s">
         <v>236</v>
@@ -20716,7 +20716,7 @@
         <v>51</v>
       </c>
       <c r="E392" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F392" t="n">
         <v>5</v>
@@ -20728,16 +20728,16 @@
         <v>92010010</v>
       </c>
       <c r="I392" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J392" t="n">
         <v>2000000</v>
       </c>
       <c r="K392" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L392" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M392" t="n">
         <v>100</v>
@@ -20760,7 +20760,7 @@
         <v>52</v>
       </c>
       <c r="E393" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F393" t="n">
         <v>5</v>
@@ -20772,16 +20772,16 @@
         <v>92010010</v>
       </c>
       <c r="I393" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J393" t="n">
         <v>2100000</v>
       </c>
       <c r="K393" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L393" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M393" t="n">
         <v>100</v>
@@ -20804,7 +20804,7 @@
         <v>53</v>
       </c>
       <c r="E394" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F394" t="n">
         <v>5</v>
@@ -20816,16 +20816,16 @@
         <v>92010010</v>
       </c>
       <c r="I394" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J394" t="n">
         <v>2200000</v>
       </c>
       <c r="K394" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L394" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M394" t="n">
         <v>100</v>
@@ -20848,7 +20848,7 @@
         <v>54</v>
       </c>
       <c r="E395" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F395" t="n">
         <v>5</v>
@@ -20860,16 +20860,16 @@
         <v>92010010</v>
       </c>
       <c r="I395" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J395" t="n">
         <v>2300000</v>
       </c>
       <c r="K395" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L395" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M395" t="n">
         <v>100</v>
@@ -20892,7 +20892,7 @@
         <v>55</v>
       </c>
       <c r="E396" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F396" t="n">
         <v>5</v>
@@ -20904,16 +20904,16 @@
         <v>92010010</v>
       </c>
       <c r="I396" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J396" t="n">
         <v>2400000</v>
       </c>
       <c r="K396" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L396" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M396" t="n">
         <v>100</v>
@@ -20936,7 +20936,7 @@
         <v>56</v>
       </c>
       <c r="E397" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F397" t="n">
         <v>5</v>
@@ -20948,16 +20948,16 @@
         <v>92010010</v>
       </c>
       <c r="I397" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J397" t="n">
         <v>2500000</v>
       </c>
       <c r="K397" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L397" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M397" t="n">
         <v>100</v>
@@ -20980,7 +20980,7 @@
         <v>57</v>
       </c>
       <c r="E398" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F398" t="n">
         <v>5</v>
@@ -20992,16 +20992,16 @@
         <v>92010010</v>
       </c>
       <c r="I398" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J398" t="n">
         <v>2600000</v>
       </c>
       <c r="K398" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L398" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M398" t="n">
         <v>100</v>
@@ -21024,7 +21024,7 @@
         <v>58</v>
       </c>
       <c r="E399" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F399" t="n">
         <v>5</v>
@@ -21036,16 +21036,16 @@
         <v>92010010</v>
       </c>
       <c r="I399" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J399" t="n">
         <v>2700000</v>
       </c>
       <c r="K399" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L399" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M399" t="n">
         <v>100</v>
@@ -21068,7 +21068,7 @@
         <v>59</v>
       </c>
       <c r="E400" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F400" t="n">
         <v>5</v>
@@ -21080,16 +21080,16 @@
         <v>92010010</v>
       </c>
       <c r="I400" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J400" t="n">
         <v>2800000</v>
       </c>
       <c r="K400" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L400" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M400" t="n">
         <v>100</v>
@@ -21112,7 +21112,7 @@
         <v>60</v>
       </c>
       <c r="E401" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F401" t="n">
         <v>5</v>
@@ -21124,16 +21124,16 @@
         <v>92010010</v>
       </c>
       <c r="I401" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J401" t="n">
         <v>2900000</v>
       </c>
       <c r="K401" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L401" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M401" t="n">
         <v>100</v>
@@ -21156,7 +21156,7 @@
         <v>61</v>
       </c>
       <c r="E402" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F402" t="n">
         <v>5</v>
@@ -21168,16 +21168,16 @@
         <v>92010010</v>
       </c>
       <c r="I402" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J402" t="n">
         <v>3000000</v>
       </c>
       <c r="K402" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L402" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M402" t="n">
         <v>100</v>
@@ -21200,7 +21200,7 @@
         <v>62</v>
       </c>
       <c r="E403" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F403" t="n">
         <v>5</v>
@@ -21212,16 +21212,16 @@
         <v>92010010</v>
       </c>
       <c r="I403" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J403" t="n">
         <v>3100000</v>
       </c>
       <c r="K403" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L403" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M403" t="n">
         <v>100</v>
@@ -21244,7 +21244,7 @@
         <v>63</v>
       </c>
       <c r="E404" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F404" t="n">
         <v>5</v>
@@ -21256,16 +21256,16 @@
         <v>92010010</v>
       </c>
       <c r="I404" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J404" t="n">
         <v>3200000</v>
       </c>
       <c r="K404" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L404" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M404" t="n">
         <v>100</v>
@@ -21288,7 +21288,7 @@
         <v>64</v>
       </c>
       <c r="E405" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F405" t="n">
         <v>5</v>
@@ -21300,16 +21300,16 @@
         <v>92010010</v>
       </c>
       <c r="I405" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J405" t="n">
         <v>3300000</v>
       </c>
       <c r="K405" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L405" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M405" t="n">
         <v>100</v>
@@ -21332,7 +21332,7 @@
         <v>65</v>
       </c>
       <c r="E406" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F406" t="n">
         <v>5</v>
@@ -21344,16 +21344,16 @@
         <v>92010010</v>
       </c>
       <c r="I406" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J406" t="n">
         <v>3400000</v>
       </c>
       <c r="K406" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L406" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M406" t="n">
         <v>100</v>
@@ -21376,7 +21376,7 @@
         <v>66</v>
       </c>
       <c r="E407" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F407" t="n">
         <v>5</v>
@@ -21388,16 +21388,16 @@
         <v>92010010</v>
       </c>
       <c r="I407" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J407" t="n">
         <v>3500000</v>
       </c>
       <c r="K407" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L407" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M407" t="n">
         <v>100</v>
@@ -21420,7 +21420,7 @@
         <v>67</v>
       </c>
       <c r="E408" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F408" t="n">
         <v>5</v>
@@ -21432,16 +21432,16 @@
         <v>92010010</v>
       </c>
       <c r="I408" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J408" t="n">
         <v>3600000</v>
       </c>
       <c r="K408" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L408" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M408" t="n">
         <v>100</v>
@@ -21464,7 +21464,7 @@
         <v>68</v>
       </c>
       <c r="E409" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F409" t="n">
         <v>5</v>
@@ -21476,16 +21476,16 @@
         <v>92010010</v>
       </c>
       <c r="I409" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J409" t="n">
         <v>3700000</v>
       </c>
       <c r="K409" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L409" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M409" t="n">
         <v>100</v>
@@ -21508,7 +21508,7 @@
         <v>69</v>
       </c>
       <c r="E410" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F410" t="n">
         <v>5</v>
@@ -21520,16 +21520,16 @@
         <v>92010010</v>
       </c>
       <c r="I410" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J410" t="n">
         <v>3800000</v>
       </c>
       <c r="K410" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L410" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M410" t="n">
         <v>100</v>
@@ -21552,7 +21552,7 @@
         <v>70</v>
       </c>
       <c r="E411" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F411" t="n">
         <v>5</v>
@@ -21564,16 +21564,16 @@
         <v>92010010</v>
       </c>
       <c r="I411" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J411" t="n">
         <v>3900000</v>
       </c>
       <c r="K411" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L411" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M411" t="n">
         <v>100</v>
@@ -21596,7 +21596,7 @@
         <v>71</v>
       </c>
       <c r="E412" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F412" t="n">
         <v>5</v>
@@ -21608,16 +21608,16 @@
         <v>92010010</v>
       </c>
       <c r="I412" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J412" t="n">
         <v>4000000</v>
       </c>
       <c r="K412" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L412" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M412" t="n">
         <v>100</v>
@@ -21640,7 +21640,7 @@
         <v>72</v>
       </c>
       <c r="E413" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F413" t="n">
         <v>5</v>
@@ -21652,16 +21652,16 @@
         <v>92010010</v>
       </c>
       <c r="I413" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J413" t="n">
         <v>4100000</v>
       </c>
       <c r="K413" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L413" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M413" t="n">
         <v>100</v>
@@ -21684,7 +21684,7 @@
         <v>73</v>
       </c>
       <c r="E414" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F414" t="n">
         <v>5</v>
@@ -21696,16 +21696,16 @@
         <v>92010010</v>
       </c>
       <c r="I414" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J414" t="n">
         <v>4200000</v>
       </c>
       <c r="K414" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L414" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M414" t="n">
         <v>100</v>
@@ -21728,7 +21728,7 @@
         <v>74</v>
       </c>
       <c r="E415" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F415" t="n">
         <v>5</v>
@@ -21740,16 +21740,16 @@
         <v>92010010</v>
       </c>
       <c r="I415" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J415" t="n">
         <v>4300000</v>
       </c>
       <c r="K415" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L415" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M415" t="n">
         <v>100</v>
@@ -21772,7 +21772,7 @@
         <v>75</v>
       </c>
       <c r="E416" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F416" t="n">
         <v>5</v>
@@ -21784,16 +21784,16 @@
         <v>92010010</v>
       </c>
       <c r="I416" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J416" t="n">
         <v>4400000</v>
       </c>
       <c r="K416" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L416" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M416" t="n">
         <v>100</v>
@@ -21816,7 +21816,7 @@
         <v>76</v>
       </c>
       <c r="E417" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F417" t="n">
         <v>5</v>
@@ -21828,16 +21828,16 @@
         <v>92010010</v>
       </c>
       <c r="I417" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J417" t="n">
         <v>4500000</v>
       </c>
       <c r="K417" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L417" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M417" t="n">
         <v>100</v>
@@ -21860,7 +21860,7 @@
         <v>77</v>
       </c>
       <c r="E418" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F418" t="n">
         <v>5</v>
@@ -21872,16 +21872,16 @@
         <v>92010010</v>
       </c>
       <c r="I418" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J418" t="n">
         <v>4600000</v>
       </c>
       <c r="K418" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L418" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M418" t="n">
         <v>100</v>
@@ -21904,7 +21904,7 @@
         <v>78</v>
       </c>
       <c r="E419" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F419" t="n">
         <v>5</v>
@@ -21916,16 +21916,16 @@
         <v>92010010</v>
       </c>
       <c r="I419" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J419" t="n">
         <v>4700000</v>
       </c>
       <c r="K419" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L419" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M419" t="n">
         <v>100</v>
@@ -21948,7 +21948,7 @@
         <v>79</v>
       </c>
       <c r="E420" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F420" t="n">
         <v>5</v>
@@ -21960,16 +21960,16 @@
         <v>92010010</v>
       </c>
       <c r="I420" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J420" t="n">
         <v>4800000</v>
       </c>
       <c r="K420" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L420" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M420" t="n">
         <v>100</v>
@@ -21992,7 +21992,7 @@
         <v>80</v>
       </c>
       <c r="E421" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F421" t="n">
         <v>5</v>
@@ -22004,7 +22004,7 @@
         <v>92010010</v>
       </c>
       <c r="I421" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J421" t="n">
         <v>4900000</v>
@@ -22013,7 +22013,7 @@
         <v>0</v>
       </c>
       <c r="L421" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M421" t="n">
         <v>0</v>
@@ -22036,7 +22036,7 @@
         <v>1</v>
       </c>
       <c r="E422" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F422" t="n">
         <v>2</v>
@@ -22054,10 +22054,10 @@
         <v>2250</v>
       </c>
       <c r="K422" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L422" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M422" t="n">
         <v>100</v>
@@ -22080,7 +22080,7 @@
         <v>2</v>
       </c>
       <c r="E423" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F423" t="n">
         <v>2</v>
@@ -22098,10 +22098,10 @@
         <v>4500</v>
       </c>
       <c r="K423" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L423" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M423" t="n">
         <v>100</v>
@@ -22124,7 +22124,7 @@
         <v>3</v>
       </c>
       <c r="E424" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F424" t="n">
         <v>2</v>
@@ -22142,10 +22142,10 @@
         <v>6750</v>
       </c>
       <c r="K424" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L424" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M424" t="n">
         <v>100</v>
@@ -22168,7 +22168,7 @@
         <v>4</v>
       </c>
       <c r="E425" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F425" t="n">
         <v>2</v>
@@ -22186,10 +22186,10 @@
         <v>9000</v>
       </c>
       <c r="K425" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L425" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M425" t="n">
         <v>100</v>
@@ -22212,7 +22212,7 @@
         <v>5</v>
       </c>
       <c r="E426" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F426" t="n">
         <v>2</v>
@@ -22230,10 +22230,10 @@
         <v>11250</v>
       </c>
       <c r="K426" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L426" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M426" t="n">
         <v>100</v>
@@ -22256,7 +22256,7 @@
         <v>6</v>
       </c>
       <c r="E427" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F427" t="n">
         <v>2</v>
@@ -22274,10 +22274,10 @@
         <v>15750</v>
       </c>
       <c r="K427" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L427" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M427" t="n">
         <v>100</v>
@@ -22300,7 +22300,7 @@
         <v>7</v>
       </c>
       <c r="E428" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F428" t="n">
         <v>2</v>
@@ -22318,10 +22318,10 @@
         <v>20250</v>
       </c>
       <c r="K428" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L428" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M428" t="n">
         <v>100</v>
@@ -22344,7 +22344,7 @@
         <v>8</v>
       </c>
       <c r="E429" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F429" t="n">
         <v>2</v>
@@ -22362,10 +22362,10 @@
         <v>24750</v>
       </c>
       <c r="K429" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L429" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M429" t="n">
         <v>100</v>
@@ -22388,7 +22388,7 @@
         <v>9</v>
       </c>
       <c r="E430" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F430" t="n">
         <v>2</v>
@@ -22406,10 +22406,10 @@
         <v>29250</v>
       </c>
       <c r="K430" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L430" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M430" t="n">
         <v>100</v>
@@ -22432,7 +22432,7 @@
         <v>10</v>
       </c>
       <c r="E431" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F431" t="n">
         <v>2</v>
@@ -22450,10 +22450,10 @@
         <v>33750</v>
       </c>
       <c r="K431" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L431" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M431" t="n">
         <v>100</v>
@@ -22476,7 +22476,7 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F432" t="n">
         <v>2</v>
@@ -22494,10 +22494,10 @@
         <v>40500</v>
       </c>
       <c r="K432" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L432" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M432" t="n">
         <v>100</v>
@@ -22520,7 +22520,7 @@
         <v>12</v>
       </c>
       <c r="E433" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F433" t="n">
         <v>2</v>
@@ -22538,10 +22538,10 @@
         <v>47250</v>
       </c>
       <c r="K433" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L433" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M433" t="n">
         <v>100</v>
@@ -22564,7 +22564,7 @@
         <v>13</v>
       </c>
       <c r="E434" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F434" t="n">
         <v>2</v>
@@ -22582,10 +22582,10 @@
         <v>54000</v>
       </c>
       <c r="K434" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L434" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M434" t="n">
         <v>100</v>
@@ -22608,7 +22608,7 @@
         <v>14</v>
       </c>
       <c r="E435" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F435" t="n">
         <v>2</v>
@@ -22626,10 +22626,10 @@
         <v>60750</v>
       </c>
       <c r="K435" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L435" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M435" t="n">
         <v>100</v>
@@ -22652,7 +22652,7 @@
         <v>15</v>
       </c>
       <c r="E436" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F436" t="n">
         <v>2</v>
@@ -22670,10 +22670,10 @@
         <v>67500</v>
       </c>
       <c r="K436" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L436" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M436" t="n">
         <v>100</v>
@@ -22696,7 +22696,7 @@
         <v>16</v>
       </c>
       <c r="E437" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F437" t="n">
         <v>2</v>
@@ -22714,10 +22714,10 @@
         <v>76500</v>
       </c>
       <c r="K437" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L437" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M437" t="n">
         <v>100</v>
@@ -22740,7 +22740,7 @@
         <v>17</v>
       </c>
       <c r="E438" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F438" t="n">
         <v>2</v>
@@ -22758,10 +22758,10 @@
         <v>85500</v>
       </c>
       <c r="K438" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L438" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M438" t="n">
         <v>100</v>
@@ -22784,7 +22784,7 @@
         <v>18</v>
       </c>
       <c r="E439" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F439" t="n">
         <v>2</v>
@@ -22802,10 +22802,10 @@
         <v>94500</v>
       </c>
       <c r="K439" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L439" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M439" t="n">
         <v>100</v>
@@ -22828,7 +22828,7 @@
         <v>19</v>
       </c>
       <c r="E440" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F440" t="n">
         <v>2</v>
@@ -22846,10 +22846,10 @@
         <v>103500</v>
       </c>
       <c r="K440" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L440" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M440" t="n">
         <v>100</v>
@@ -22872,7 +22872,7 @@
         <v>20</v>
       </c>
       <c r="E441" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F441" t="n">
         <v>2</v>
@@ -22893,7 +22893,7 @@
         <v>98</v>
       </c>
       <c r="L441" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M441" t="n">
         <v>0</v>
@@ -22916,7 +22916,7 @@
         <v>1</v>
       </c>
       <c r="E442" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F442" t="n">
         <v>3</v>
@@ -22934,10 +22934,10 @@
         <v>4500</v>
       </c>
       <c r="K442" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L442" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M442" t="n">
         <v>100</v>
@@ -22960,7 +22960,7 @@
         <v>2</v>
       </c>
       <c r="E443" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F443" t="n">
         <v>3</v>
@@ -22978,10 +22978,10 @@
         <v>9000</v>
       </c>
       <c r="K443" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L443" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M443" t="n">
         <v>100</v>
@@ -23004,7 +23004,7 @@
         <v>3</v>
       </c>
       <c r="E444" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F444" t="n">
         <v>3</v>
@@ -23022,10 +23022,10 @@
         <v>13500</v>
       </c>
       <c r="K444" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L444" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M444" t="n">
         <v>100</v>
@@ -23048,7 +23048,7 @@
         <v>4</v>
       </c>
       <c r="E445" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F445" t="n">
         <v>3</v>
@@ -23066,10 +23066,10 @@
         <v>18000</v>
       </c>
       <c r="K445" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L445" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M445" t="n">
         <v>100</v>
@@ -23092,7 +23092,7 @@
         <v>5</v>
       </c>
       <c r="E446" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F446" t="n">
         <v>3</v>
@@ -23110,10 +23110,10 @@
         <v>22500</v>
       </c>
       <c r="K446" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L446" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M446" t="n">
         <v>100</v>
@@ -23136,7 +23136,7 @@
         <v>6</v>
       </c>
       <c r="E447" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F447" t="n">
         <v>3</v>
@@ -23154,10 +23154,10 @@
         <v>31500</v>
       </c>
       <c r="K447" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L447" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M447" t="n">
         <v>100</v>
@@ -23180,7 +23180,7 @@
         <v>7</v>
       </c>
       <c r="E448" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F448" t="n">
         <v>3</v>
@@ -23198,10 +23198,10 @@
         <v>40500</v>
       </c>
       <c r="K448" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L448" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M448" t="n">
         <v>100</v>
@@ -23224,7 +23224,7 @@
         <v>8</v>
       </c>
       <c r="E449" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F449" t="n">
         <v>3</v>
@@ -23242,10 +23242,10 @@
         <v>49500</v>
       </c>
       <c r="K449" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L449" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M449" t="n">
         <v>100</v>
@@ -23268,7 +23268,7 @@
         <v>9</v>
       </c>
       <c r="E450" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F450" t="n">
         <v>3</v>
@@ -23286,10 +23286,10 @@
         <v>58500</v>
       </c>
       <c r="K450" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L450" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M450" t="n">
         <v>100</v>
@@ -23312,7 +23312,7 @@
         <v>10</v>
       </c>
       <c r="E451" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F451" t="n">
         <v>3</v>
@@ -23330,10 +23330,10 @@
         <v>67500</v>
       </c>
       <c r="K451" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L451" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M451" t="n">
         <v>100</v>
@@ -23356,7 +23356,7 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F452" t="n">
         <v>3</v>
@@ -23374,10 +23374,10 @@
         <v>81000</v>
       </c>
       <c r="K452" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L452" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M452" t="n">
         <v>100</v>
@@ -23400,7 +23400,7 @@
         <v>12</v>
       </c>
       <c r="E453" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F453" t="n">
         <v>3</v>
@@ -23418,10 +23418,10 @@
         <v>94500</v>
       </c>
       <c r="K453" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L453" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M453" t="n">
         <v>100</v>
@@ -23444,7 +23444,7 @@
         <v>13</v>
       </c>
       <c r="E454" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F454" t="n">
         <v>3</v>
@@ -23462,10 +23462,10 @@
         <v>108000</v>
       </c>
       <c r="K454" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L454" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M454" t="n">
         <v>100</v>
@@ -23488,7 +23488,7 @@
         <v>14</v>
       </c>
       <c r="E455" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F455" t="n">
         <v>3</v>
@@ -23506,10 +23506,10 @@
         <v>121500</v>
       </c>
       <c r="K455" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L455" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M455" t="n">
         <v>100</v>
@@ -23532,7 +23532,7 @@
         <v>15</v>
       </c>
       <c r="E456" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F456" t="n">
         <v>3</v>
@@ -23550,10 +23550,10 @@
         <v>135000</v>
       </c>
       <c r="K456" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L456" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M456" t="n">
         <v>100</v>
@@ -23576,7 +23576,7 @@
         <v>16</v>
       </c>
       <c r="E457" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F457" t="n">
         <v>3</v>
@@ -23594,10 +23594,10 @@
         <v>153000</v>
       </c>
       <c r="K457" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L457" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M457" t="n">
         <v>100</v>
@@ -23620,7 +23620,7 @@
         <v>17</v>
       </c>
       <c r="E458" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F458" t="n">
         <v>3</v>
@@ -23638,10 +23638,10 @@
         <v>171000</v>
       </c>
       <c r="K458" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L458" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M458" t="n">
         <v>100</v>
@@ -23664,7 +23664,7 @@
         <v>18</v>
       </c>
       <c r="E459" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F459" t="n">
         <v>3</v>
@@ -23682,10 +23682,10 @@
         <v>189000</v>
       </c>
       <c r="K459" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L459" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M459" t="n">
         <v>100</v>
@@ -23708,7 +23708,7 @@
         <v>19</v>
       </c>
       <c r="E460" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F460" t="n">
         <v>3</v>
@@ -23726,10 +23726,10 @@
         <v>207000</v>
       </c>
       <c r="K460" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L460" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M460" t="n">
         <v>100</v>
@@ -23752,7 +23752,7 @@
         <v>20</v>
       </c>
       <c r="E461" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F461" t="n">
         <v>3</v>
@@ -23773,7 +23773,7 @@
         <v>98</v>
       </c>
       <c r="L461" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M461" t="n">
         <v>0</v>
@@ -23796,7 +23796,7 @@
         <v>1</v>
       </c>
       <c r="E462" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F462" t="n">
         <v>4</v>
@@ -23814,10 +23814,10 @@
         <v>6750</v>
       </c>
       <c r="K462" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L462" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M462" t="n">
         <v>100</v>
@@ -23840,7 +23840,7 @@
         <v>2</v>
       </c>
       <c r="E463" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F463" t="n">
         <v>4</v>
@@ -23858,10 +23858,10 @@
         <v>13500</v>
       </c>
       <c r="K463" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L463" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M463" t="n">
         <v>100</v>
@@ -23884,7 +23884,7 @@
         <v>3</v>
       </c>
       <c r="E464" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F464" t="n">
         <v>4</v>
@@ -23902,10 +23902,10 @@
         <v>20250</v>
       </c>
       <c r="K464" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L464" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M464" t="n">
         <v>100</v>
@@ -23928,7 +23928,7 @@
         <v>4</v>
       </c>
       <c r="E465" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F465" t="n">
         <v>4</v>
@@ -23946,10 +23946,10 @@
         <v>27000</v>
       </c>
       <c r="K465" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L465" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M465" t="n">
         <v>100</v>
@@ -23972,7 +23972,7 @@
         <v>5</v>
       </c>
       <c r="E466" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F466" t="n">
         <v>4</v>
@@ -23990,10 +23990,10 @@
         <v>33750</v>
       </c>
       <c r="K466" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L466" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M466" t="n">
         <v>100</v>
@@ -24016,7 +24016,7 @@
         <v>6</v>
       </c>
       <c r="E467" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F467" t="n">
         <v>4</v>
@@ -24034,10 +24034,10 @@
         <v>47250</v>
       </c>
       <c r="K467" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L467" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M467" t="n">
         <v>100</v>
@@ -24060,7 +24060,7 @@
         <v>7</v>
       </c>
       <c r="E468" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F468" t="n">
         <v>4</v>
@@ -24078,10 +24078,10 @@
         <v>60750</v>
       </c>
       <c r="K468" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L468" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M468" t="n">
         <v>100</v>
@@ -24104,7 +24104,7 @@
         <v>8</v>
       </c>
       <c r="E469" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F469" t="n">
         <v>4</v>
@@ -24122,10 +24122,10 @@
         <v>74250</v>
       </c>
       <c r="K469" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L469" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M469" t="n">
         <v>100</v>
@@ -24148,7 +24148,7 @@
         <v>9</v>
       </c>
       <c r="E470" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F470" t="n">
         <v>4</v>
@@ -24166,10 +24166,10 @@
         <v>87750</v>
       </c>
       <c r="K470" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L470" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M470" t="n">
         <v>100</v>
@@ -24192,7 +24192,7 @@
         <v>10</v>
       </c>
       <c r="E471" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F471" t="n">
         <v>4</v>
@@ -24210,10 +24210,10 @@
         <v>101250</v>
       </c>
       <c r="K471" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L471" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M471" t="n">
         <v>100</v>
@@ -24236,7 +24236,7 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F472" t="n">
         <v>4</v>
@@ -24254,10 +24254,10 @@
         <v>121500</v>
       </c>
       <c r="K472" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L472" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M472" t="n">
         <v>100</v>
@@ -24280,7 +24280,7 @@
         <v>12</v>
       </c>
       <c r="E473" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F473" t="n">
         <v>4</v>
@@ -24298,10 +24298,10 @@
         <v>141750</v>
       </c>
       <c r="K473" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L473" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M473" t="n">
         <v>100</v>
@@ -24324,7 +24324,7 @@
         <v>13</v>
       </c>
       <c r="E474" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F474" t="n">
         <v>4</v>
@@ -24342,10 +24342,10 @@
         <v>162000</v>
       </c>
       <c r="K474" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L474" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M474" t="n">
         <v>100</v>
@@ -24368,7 +24368,7 @@
         <v>14</v>
       </c>
       <c r="E475" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F475" t="n">
         <v>4</v>
@@ -24386,10 +24386,10 @@
         <v>182250</v>
       </c>
       <c r="K475" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L475" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M475" t="n">
         <v>100</v>
@@ -24412,7 +24412,7 @@
         <v>15</v>
       </c>
       <c r="E476" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F476" t="n">
         <v>4</v>
@@ -24430,10 +24430,10 @@
         <v>202500</v>
       </c>
       <c r="K476" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L476" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M476" t="n">
         <v>100</v>
@@ -24456,7 +24456,7 @@
         <v>16</v>
       </c>
       <c r="E477" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F477" t="n">
         <v>4</v>
@@ -24474,10 +24474,10 @@
         <v>229500</v>
       </c>
       <c r="K477" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L477" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M477" t="n">
         <v>100</v>
@@ -24500,7 +24500,7 @@
         <v>17</v>
       </c>
       <c r="E478" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F478" t="n">
         <v>4</v>
@@ -24518,10 +24518,10 @@
         <v>256500</v>
       </c>
       <c r="K478" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L478" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M478" t="n">
         <v>100</v>
@@ -24544,7 +24544,7 @@
         <v>18</v>
       </c>
       <c r="E479" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F479" t="n">
         <v>4</v>
@@ -24562,10 +24562,10 @@
         <v>283500</v>
       </c>
       <c r="K479" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L479" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M479" t="n">
         <v>100</v>
@@ -24588,7 +24588,7 @@
         <v>19</v>
       </c>
       <c r="E480" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F480" t="n">
         <v>4</v>
@@ -24606,10 +24606,10 @@
         <v>310500</v>
       </c>
       <c r="K480" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L480" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M480" t="n">
         <v>100</v>
@@ -24632,7 +24632,7 @@
         <v>20</v>
       </c>
       <c r="E481" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F481" t="n">
         <v>4</v>
@@ -24653,7 +24653,7 @@
         <v>98</v>
       </c>
       <c r="L481" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M481" t="n">
         <v>0</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="E482" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F482" t="n">
         <v>5</v>
@@ -24720,7 +24720,7 @@
         <v>2</v>
       </c>
       <c r="E483" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F483" t="n">
         <v>5</v>
@@ -24764,7 +24764,7 @@
         <v>3</v>
       </c>
       <c r="E484" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F484" t="n">
         <v>5</v>
@@ -24808,7 +24808,7 @@
         <v>4</v>
       </c>
       <c r="E485" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F485" t="n">
         <v>5</v>
@@ -24852,7 +24852,7 @@
         <v>5</v>
       </c>
       <c r="E486" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F486" t="n">
         <v>5</v>
@@ -24896,7 +24896,7 @@
         <v>6</v>
       </c>
       <c r="E487" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F487" t="n">
         <v>5</v>
@@ -24940,7 +24940,7 @@
         <v>7</v>
       </c>
       <c r="E488" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F488" t="n">
         <v>5</v>
@@ -24984,7 +24984,7 @@
         <v>8</v>
       </c>
       <c r="E489" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F489" t="n">
         <v>5</v>
@@ -25028,7 +25028,7 @@
         <v>9</v>
       </c>
       <c r="E490" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F490" t="n">
         <v>5</v>
@@ -25072,7 +25072,7 @@
         <v>10</v>
       </c>
       <c r="E491" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F491" t="n">
         <v>5</v>
@@ -25116,7 +25116,7 @@
         <v>11</v>
       </c>
       <c r="E492" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F492" t="n">
         <v>5</v>
@@ -25160,7 +25160,7 @@
         <v>12</v>
       </c>
       <c r="E493" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F493" t="n">
         <v>5</v>
@@ -25204,7 +25204,7 @@
         <v>13</v>
       </c>
       <c r="E494" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F494" t="n">
         <v>5</v>
@@ -25248,7 +25248,7 @@
         <v>14</v>
       </c>
       <c r="E495" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F495" t="n">
         <v>5</v>
@@ -25292,7 +25292,7 @@
         <v>15</v>
       </c>
       <c r="E496" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F496" t="n">
         <v>5</v>
@@ -25336,7 +25336,7 @@
         <v>16</v>
       </c>
       <c r="E497" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F497" t="n">
         <v>5</v>
@@ -25380,7 +25380,7 @@
         <v>17</v>
       </c>
       <c r="E498" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F498" t="n">
         <v>5</v>
@@ -25424,7 +25424,7 @@
         <v>18</v>
       </c>
       <c r="E499" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F499" t="n">
         <v>5</v>
@@ -25468,7 +25468,7 @@
         <v>19</v>
       </c>
       <c r="E500" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F500" t="n">
         <v>5</v>
@@ -25512,7 +25512,7 @@
         <v>20</v>
       </c>
       <c r="E501" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F501" t="n">
         <v>5</v>
@@ -25556,7 +25556,7 @@
         <v>21</v>
       </c>
       <c r="E502" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F502" t="n">
         <v>5</v>
@@ -25600,7 +25600,7 @@
         <v>22</v>
       </c>
       <c r="E503" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F503" t="n">
         <v>5</v>
@@ -25644,7 +25644,7 @@
         <v>23</v>
       </c>
       <c r="E504" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F504" t="n">
         <v>5</v>
@@ -25688,7 +25688,7 @@
         <v>24</v>
       </c>
       <c r="E505" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F505" t="n">
         <v>5</v>
@@ -25732,7 +25732,7 @@
         <v>25</v>
       </c>
       <c r="E506" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F506" t="n">
         <v>5</v>
@@ -25776,7 +25776,7 @@
         <v>26</v>
       </c>
       <c r="E507" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F507" t="n">
         <v>5</v>
@@ -25820,7 +25820,7 @@
         <v>27</v>
       </c>
       <c r="E508" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F508" t="n">
         <v>5</v>
@@ -25864,7 +25864,7 @@
         <v>28</v>
       </c>
       <c r="E509" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F509" t="n">
         <v>5</v>
@@ -25908,7 +25908,7 @@
         <v>29</v>
       </c>
       <c r="E510" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F510" t="n">
         <v>5</v>
@@ -25952,7 +25952,7 @@
         <v>30</v>
       </c>
       <c r="E511" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F511" t="n">
         <v>5</v>
@@ -25996,7 +25996,7 @@
         <v>31</v>
       </c>
       <c r="E512" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F512" t="n">
         <v>5</v>
@@ -26040,7 +26040,7 @@
         <v>32</v>
       </c>
       <c r="E513" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F513" t="n">
         <v>5</v>
@@ -26084,7 +26084,7 @@
         <v>33</v>
       </c>
       <c r="E514" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F514" t="n">
         <v>5</v>
@@ -26128,7 +26128,7 @@
         <v>34</v>
       </c>
       <c r="E515" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F515" t="n">
         <v>5</v>
@@ -26172,7 +26172,7 @@
         <v>35</v>
       </c>
       <c r="E516" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F516" t="n">
         <v>5</v>
@@ -26216,7 +26216,7 @@
         <v>36</v>
       </c>
       <c r="E517" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F517" t="n">
         <v>5</v>
@@ -26260,7 +26260,7 @@
         <v>37</v>
       </c>
       <c r="E518" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F518" t="n">
         <v>5</v>
@@ -26304,7 +26304,7 @@
         <v>38</v>
       </c>
       <c r="E519" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F519" t="n">
         <v>5</v>
@@ -26348,7 +26348,7 @@
         <v>39</v>
       </c>
       <c r="E520" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F520" t="n">
         <v>5</v>
@@ -26392,7 +26392,7 @@
         <v>40</v>
       </c>
       <c r="E521" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F521" t="n">
         <v>5</v>
@@ -26436,7 +26436,7 @@
         <v>41</v>
       </c>
       <c r="E522" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F522" t="n">
         <v>5</v>
@@ -26480,7 +26480,7 @@
         <v>42</v>
       </c>
       <c r="E523" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F523" t="n">
         <v>5</v>
@@ -26524,7 +26524,7 @@
         <v>43</v>
       </c>
       <c r="E524" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F524" t="n">
         <v>5</v>
@@ -26568,7 +26568,7 @@
         <v>44</v>
       </c>
       <c r="E525" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F525" t="n">
         <v>5</v>
@@ -26612,7 +26612,7 @@
         <v>45</v>
       </c>
       <c r="E526" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F526" t="n">
         <v>5</v>
@@ -26656,7 +26656,7 @@
         <v>46</v>
       </c>
       <c r="E527" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F527" t="n">
         <v>5</v>
@@ -26700,7 +26700,7 @@
         <v>47</v>
       </c>
       <c r="E528" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F528" t="n">
         <v>5</v>
@@ -26744,7 +26744,7 @@
         <v>48</v>
       </c>
       <c r="E529" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F529" t="n">
         <v>5</v>
@@ -26788,7 +26788,7 @@
         <v>49</v>
       </c>
       <c r="E530" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F530" t="n">
         <v>5</v>
@@ -26832,7 +26832,7 @@
         <v>50</v>
       </c>
       <c r="E531" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F531" t="n">
         <v>5</v>
@@ -26876,7 +26876,7 @@
         <v>51</v>
       </c>
       <c r="E532" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F532" t="n">
         <v>5</v>
@@ -26888,7 +26888,7 @@
         <v>92010010</v>
       </c>
       <c r="I532" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J532" t="n">
         <v>2000000</v>
@@ -26897,7 +26897,7 @@
         <v>687</v>
       </c>
       <c r="L532" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M532" t="n">
         <v>100</v>
@@ -26920,7 +26920,7 @@
         <v>52</v>
       </c>
       <c r="E533" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F533" t="n">
         <v>5</v>
@@ -26932,7 +26932,7 @@
         <v>92010010</v>
       </c>
       <c r="I533" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J533" t="n">
         <v>2100000</v>
@@ -26941,7 +26941,7 @@
         <v>688</v>
       </c>
       <c r="L533" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M533" t="n">
         <v>100</v>
@@ -26964,7 +26964,7 @@
         <v>53</v>
       </c>
       <c r="E534" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F534" t="n">
         <v>5</v>
@@ -26976,7 +26976,7 @@
         <v>92010010</v>
       </c>
       <c r="I534" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J534" t="n">
         <v>2200000</v>
@@ -26985,7 +26985,7 @@
         <v>689</v>
       </c>
       <c r="L534" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M534" t="n">
         <v>100</v>
@@ -27008,7 +27008,7 @@
         <v>54</v>
       </c>
       <c r="E535" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F535" t="n">
         <v>5</v>
@@ -27020,7 +27020,7 @@
         <v>92010010</v>
       </c>
       <c r="I535" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J535" t="n">
         <v>2300000</v>
@@ -27029,7 +27029,7 @@
         <v>690</v>
       </c>
       <c r="L535" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M535" t="n">
         <v>100</v>
@@ -27052,7 +27052,7 @@
         <v>55</v>
       </c>
       <c r="E536" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F536" t="n">
         <v>5</v>
@@ -27064,7 +27064,7 @@
         <v>92010010</v>
       </c>
       <c r="I536" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J536" t="n">
         <v>2400000</v>
@@ -27073,7 +27073,7 @@
         <v>691</v>
       </c>
       <c r="L536" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M536" t="n">
         <v>100</v>
@@ -27096,7 +27096,7 @@
         <v>56</v>
       </c>
       <c r="E537" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F537" t="n">
         <v>5</v>
@@ -27108,7 +27108,7 @@
         <v>92010010</v>
       </c>
       <c r="I537" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J537" t="n">
         <v>2500000</v>
@@ -27117,7 +27117,7 @@
         <v>692</v>
       </c>
       <c r="L537" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M537" t="n">
         <v>100</v>
@@ -27140,7 +27140,7 @@
         <v>57</v>
       </c>
       <c r="E538" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F538" t="n">
         <v>5</v>
@@ -27152,7 +27152,7 @@
         <v>92010010</v>
       </c>
       <c r="I538" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J538" t="n">
         <v>2600000</v>
@@ -27161,7 +27161,7 @@
         <v>693</v>
       </c>
       <c r="L538" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M538" t="n">
         <v>100</v>
@@ -27184,7 +27184,7 @@
         <v>58</v>
       </c>
       <c r="E539" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F539" t="n">
         <v>5</v>
@@ -27196,7 +27196,7 @@
         <v>92010010</v>
       </c>
       <c r="I539" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J539" t="n">
         <v>2700000</v>
@@ -27205,7 +27205,7 @@
         <v>694</v>
       </c>
       <c r="L539" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M539" t="n">
         <v>100</v>
@@ -27228,7 +27228,7 @@
         <v>59</v>
       </c>
       <c r="E540" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F540" t="n">
         <v>5</v>
@@ -27240,7 +27240,7 @@
         <v>92010010</v>
       </c>
       <c r="I540" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J540" t="n">
         <v>2800000</v>
@@ -27249,7 +27249,7 @@
         <v>695</v>
       </c>
       <c r="L540" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M540" t="n">
         <v>100</v>
@@ -27272,7 +27272,7 @@
         <v>60</v>
       </c>
       <c r="E541" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F541" t="n">
         <v>5</v>
@@ -27284,7 +27284,7 @@
         <v>92010010</v>
       </c>
       <c r="I541" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J541" t="n">
         <v>2900000</v>
@@ -27293,7 +27293,7 @@
         <v>696</v>
       </c>
       <c r="L541" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M541" t="n">
         <v>100</v>
@@ -27316,7 +27316,7 @@
         <v>61</v>
       </c>
       <c r="E542" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F542" t="n">
         <v>5</v>
@@ -27328,7 +27328,7 @@
         <v>92010010</v>
       </c>
       <c r="I542" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J542" t="n">
         <v>3000000</v>
@@ -27337,7 +27337,7 @@
         <v>697</v>
       </c>
       <c r="L542" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M542" t="n">
         <v>100</v>
@@ -27360,7 +27360,7 @@
         <v>62</v>
       </c>
       <c r="E543" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F543" t="n">
         <v>5</v>
@@ -27372,7 +27372,7 @@
         <v>92010010</v>
       </c>
       <c r="I543" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J543" t="n">
         <v>3100000</v>
@@ -27381,7 +27381,7 @@
         <v>698</v>
       </c>
       <c r="L543" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M543" t="n">
         <v>100</v>
@@ -27404,7 +27404,7 @@
         <v>63</v>
       </c>
       <c r="E544" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F544" t="n">
         <v>5</v>
@@ -27416,7 +27416,7 @@
         <v>92010010</v>
       </c>
       <c r="I544" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J544" t="n">
         <v>3200000</v>
@@ -27425,7 +27425,7 @@
         <v>699</v>
       </c>
       <c r="L544" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M544" t="n">
         <v>100</v>
@@ -27448,7 +27448,7 @@
         <v>64</v>
       </c>
       <c r="E545" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F545" t="n">
         <v>5</v>
@@ -27460,7 +27460,7 @@
         <v>92010010</v>
       </c>
       <c r="I545" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J545" t="n">
         <v>3300000</v>
@@ -27469,7 +27469,7 @@
         <v>700</v>
       </c>
       <c r="L545" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M545" t="n">
         <v>100</v>
@@ -27492,7 +27492,7 @@
         <v>65</v>
       </c>
       <c r="E546" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F546" t="n">
         <v>5</v>
@@ -27504,7 +27504,7 @@
         <v>92010010</v>
       </c>
       <c r="I546" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J546" t="n">
         <v>3400000</v>
@@ -27513,7 +27513,7 @@
         <v>701</v>
       </c>
       <c r="L546" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M546" t="n">
         <v>100</v>
@@ -27536,7 +27536,7 @@
         <v>66</v>
       </c>
       <c r="E547" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F547" t="n">
         <v>5</v>
@@ -27548,7 +27548,7 @@
         <v>92010010</v>
       </c>
       <c r="I547" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J547" t="n">
         <v>3500000</v>
@@ -27557,7 +27557,7 @@
         <v>702</v>
       </c>
       <c r="L547" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M547" t="n">
         <v>100</v>
@@ -27580,7 +27580,7 @@
         <v>67</v>
       </c>
       <c r="E548" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F548" t="n">
         <v>5</v>
@@ -27592,7 +27592,7 @@
         <v>92010010</v>
       </c>
       <c r="I548" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J548" t="n">
         <v>3600000</v>
@@ -27601,7 +27601,7 @@
         <v>703</v>
       </c>
       <c r="L548" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M548" t="n">
         <v>100</v>
@@ -27624,7 +27624,7 @@
         <v>68</v>
       </c>
       <c r="E549" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F549" t="n">
         <v>5</v>
@@ -27636,7 +27636,7 @@
         <v>92010010</v>
       </c>
       <c r="I549" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J549" t="n">
         <v>3700000</v>
@@ -27645,7 +27645,7 @@
         <v>704</v>
       </c>
       <c r="L549" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M549" t="n">
         <v>100</v>
@@ -27668,7 +27668,7 @@
         <v>69</v>
       </c>
       <c r="E550" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F550" t="n">
         <v>5</v>
@@ -27680,7 +27680,7 @@
         <v>92010010</v>
       </c>
       <c r="I550" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J550" t="n">
         <v>3800000</v>
@@ -27689,7 +27689,7 @@
         <v>705</v>
       </c>
       <c r="L550" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M550" t="n">
         <v>100</v>
@@ -27712,7 +27712,7 @@
         <v>70</v>
       </c>
       <c r="E551" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F551" t="n">
         <v>5</v>
@@ -27724,7 +27724,7 @@
         <v>92010010</v>
       </c>
       <c r="I551" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J551" t="n">
         <v>3900000</v>
@@ -27733,7 +27733,7 @@
         <v>706</v>
       </c>
       <c r="L551" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M551" t="n">
         <v>100</v>
@@ -27756,7 +27756,7 @@
         <v>71</v>
       </c>
       <c r="E552" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F552" t="n">
         <v>5</v>
@@ -27768,7 +27768,7 @@
         <v>92010010</v>
       </c>
       <c r="I552" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J552" t="n">
         <v>4000000</v>
@@ -27777,7 +27777,7 @@
         <v>707</v>
       </c>
       <c r="L552" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M552" t="n">
         <v>100</v>
@@ -27800,7 +27800,7 @@
         <v>72</v>
       </c>
       <c r="E553" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F553" t="n">
         <v>5</v>
@@ -27812,7 +27812,7 @@
         <v>92010010</v>
       </c>
       <c r="I553" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J553" t="n">
         <v>4100000</v>
@@ -27821,7 +27821,7 @@
         <v>708</v>
       </c>
       <c r="L553" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M553" t="n">
         <v>100</v>
@@ -27844,7 +27844,7 @@
         <v>73</v>
       </c>
       <c r="E554" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F554" t="n">
         <v>5</v>
@@ -27856,7 +27856,7 @@
         <v>92010010</v>
       </c>
       <c r="I554" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J554" t="n">
         <v>4200000</v>
@@ -27865,7 +27865,7 @@
         <v>709</v>
       </c>
       <c r="L554" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M554" t="n">
         <v>100</v>
@@ -27888,7 +27888,7 @@
         <v>74</v>
       </c>
       <c r="E555" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F555" t="n">
         <v>5</v>
@@ -27900,7 +27900,7 @@
         <v>92010010</v>
       </c>
       <c r="I555" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J555" t="n">
         <v>4300000</v>
@@ -27909,7 +27909,7 @@
         <v>710</v>
       </c>
       <c r="L555" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M555" t="n">
         <v>100</v>
@@ -27932,7 +27932,7 @@
         <v>75</v>
       </c>
       <c r="E556" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F556" t="n">
         <v>5</v>
@@ -27944,7 +27944,7 @@
         <v>92010010</v>
       </c>
       <c r="I556" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J556" t="n">
         <v>4400000</v>
@@ -27953,7 +27953,7 @@
         <v>711</v>
       </c>
       <c r="L556" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M556" t="n">
         <v>100</v>
@@ -27976,7 +27976,7 @@
         <v>76</v>
       </c>
       <c r="E557" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F557" t="n">
         <v>5</v>
@@ -27988,7 +27988,7 @@
         <v>92010010</v>
       </c>
       <c r="I557" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J557" t="n">
         <v>4500000</v>
@@ -27997,7 +27997,7 @@
         <v>712</v>
       </c>
       <c r="L557" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M557" t="n">
         <v>100</v>
@@ -28020,7 +28020,7 @@
         <v>77</v>
       </c>
       <c r="E558" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F558" t="n">
         <v>5</v>
@@ -28032,7 +28032,7 @@
         <v>92010010</v>
       </c>
       <c r="I558" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J558" t="n">
         <v>4600000</v>
@@ -28041,7 +28041,7 @@
         <v>713</v>
       </c>
       <c r="L558" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M558" t="n">
         <v>100</v>
@@ -28064,7 +28064,7 @@
         <v>78</v>
       </c>
       <c r="E559" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F559" t="n">
         <v>5</v>
@@ -28076,7 +28076,7 @@
         <v>92010010</v>
       </c>
       <c r="I559" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J559" t="n">
         <v>4700000</v>
@@ -28085,7 +28085,7 @@
         <v>714</v>
       </c>
       <c r="L559" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M559" t="n">
         <v>100</v>
@@ -28108,7 +28108,7 @@
         <v>79</v>
       </c>
       <c r="E560" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F560" t="n">
         <v>5</v>
@@ -28120,7 +28120,7 @@
         <v>92010010</v>
       </c>
       <c r="I560" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J560" t="n">
         <v>4800000</v>
@@ -28129,7 +28129,7 @@
         <v>715</v>
       </c>
       <c r="L560" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M560" t="n">
         <v>100</v>
@@ -28152,7 +28152,7 @@
         <v>80</v>
       </c>
       <c r="E561" t="s">
-        <v>661</v>
+        <v>237</v>
       </c>
       <c r="F561" t="n">
         <v>5</v>
@@ -28164,7 +28164,7 @@
         <v>92010010</v>
       </c>
       <c r="I561" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J561" t="n">
         <v>4900000</v>
@@ -28173,7 +28173,7 @@
         <v>0</v>
       </c>
       <c r="L561" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M561" t="n">
         <v>0</v>
